--- a/DataTables/Datas/battle.card.xlsx
+++ b/DataTables/Datas/battle.card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF38928-3842-4817-9C38-37E7729A7AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9799F2C3-22AD-45D4-81C0-796172DCEFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="0" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -42,9 +42,6 @@
     <t>target_rule</t>
   </si>
   <si>
-    <t>effect_id</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -75,13 +72,46 @@
     <t>Target rule</t>
   </si>
   <si>
-    <t>Effect ID</t>
+    <t>effect_ids</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect ID list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Strength</t>
   </si>
   <si>
     <t>Self</t>
+  </si>
+  <si>
+    <t>4001</t>
+  </si>
+  <si>
+    <t>Strike</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>4002</t>
+  </si>
+  <si>
+    <t>Defend</t>
+  </si>
+  <si>
+    <t>4003</t>
+  </si>
+  <si>
+    <t>Bash</t>
+  </si>
+  <si>
+    <t>4004,4005</t>
   </si>
 </sst>
 </file>
@@ -127,8 +157,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -473,52 +506,52 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -526,17 +559,104 @@
         <v>3001</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>4001</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>3002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>3003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>3004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/DataTables/Datas/battle.card.xlsx
+++ b/DataTables/Datas/battle.card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9799F2C3-22AD-45D4-81C0-796172DCEFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEDBAEC-851A-485A-9931-293526BD88A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -33,9 +33,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>cost</t>
   </si>
   <si>
@@ -63,55 +60,90 @@
     <t>Unique ID</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>Cost</t>
   </si>
   <si>
     <t>Target rule</t>
   </si>
   <si>
-    <t>effect_ids</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(array#sep=,),int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Effect ID list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strength</t>
-  </si>
-  <si>
     <t>Self</t>
   </si>
   <si>
-    <t>4001</t>
-  </si>
-  <si>
-    <t>Strike</t>
-  </si>
-  <si>
     <t>Enemy</t>
   </si>
   <si>
-    <t>4002</t>
-  </si>
-  <si>
-    <t>Defend</t>
-  </si>
-  <si>
-    <t>4003</t>
-  </si>
-  <si>
-    <t>Bash</t>
-  </si>
-  <si>
-    <t>4004,4005</t>
+    <t>name_i18n_key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>description_i18n_key</t>
+  </si>
+  <si>
+    <t>effect_bindings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=,),battle.CardEffectBinding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name localization key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description localization key</t>
+  </si>
+  <si>
+    <t>Ordered effect argument bindings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.strength.name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.strength.description</t>
+  </si>
+  <si>
+    <t>strength:4001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.strike.name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.strike.description</t>
+  </si>
+  <si>
+    <t>damage:4002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.defend.name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.defend.description</t>
+  </si>
+  <si>
+    <t>block:4003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.bash.name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.bash.description</t>
+  </si>
+  <si>
+    <t>damage:4004,vulnerable:4005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -478,18 +510,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.625" customWidth="1"/>
+    <col min="4" max="4" width="42.625" customWidth="1"/>
+    <col min="5" max="5" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,166 +530,187 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>3001</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>3002</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3003</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>3004</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F20" s="1"/>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/DataTables/Datas/battle.card.xlsx
+++ b/DataTables/Datas/battle.card.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -144,13 +144,31 @@
   <si>
     <t>damage:4004,vulnerable:4005</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>illustration_address</t>
+  </si>
+  <si>
+    <t>Full Assets/... sprite address</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Runtime/Card/card_art_strength.png</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Runtime/Card/card_art_strike.png</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Runtime/Card/card_art_defend.png</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Runtime/Card/card_art_bash.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,13 +184,123 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F9F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF9EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F4FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF5F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7EFCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFE7F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E9E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F1F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -189,11 +317,77 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -510,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -520,197 +714,231 @@
     <col min="5" max="5" width="5.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.625" customWidth="1"/>
+    <col min="8" max="8" width="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="2">
         <v>17</v>
       </c>
+      <c r="H1" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="3">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="3">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="3">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="3">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="3">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="3">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="3">
         <v>19</v>
       </c>
+      <c r="H2" t="s" s="3">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="5">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="5">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="5">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="5">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="5">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="5">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="5">
         <v>22</v>
       </c>
+      <c r="H4" t="s" s="5">
+        <v>36</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="10">
         <v>3001</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="11">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="12">
         <v>24</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="13">
         <v>0</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="14">
         <v>13</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="15" t="s">
         <v>25</v>
       </c>
+      <c r="H5" t="s" s="16">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6">
+      <c r="B6" s="17">
         <v>3002</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="18">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="19">
         <v>27</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="20">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="21">
         <v>14</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="22" t="s">
         <v>28</v>
       </c>
+      <c r="H6" t="s" s="23">
+        <v>38</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7">
+      <c r="B7" s="10">
         <v>3003</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="11">
         <v>29</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="13">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="14">
         <v>13</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="15" t="s">
         <v>31</v>
       </c>
+      <c r="H7" t="s" s="16">
+        <v>39</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8">
+      <c r="B8" s="17">
         <v>3004</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="18">
         <v>32</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="19">
         <v>33</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="20">
         <v>2</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="21">
         <v>14</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="22" t="s">
         <v>34</v>
+      </c>
+      <c r="H8" t="s" s="23">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
     <row r="17" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
     </row>
     <row r="18" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
     <row r="19" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
     <row r="20" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/DataTables/Datas/battle.card.xlsx
+++ b/DataTables/Datas/battle.card.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re95ce1a15d69406b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2eb378f8f274ecd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,8 +41,14 @@
       <x:color rgb="FF5B4B00"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,6 +80,51 @@
         <x:fgColor rgb="FFF7F7F7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F7F7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -81,7 +132,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -154,6 +205,110 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -398,6 +553,8 @@
     <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="32" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="28" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -458,6 +615,12 @@
       <x:c r="S1" s="9" t="str">
         <x:v>illustration_key</x:v>
       </x:c>
+      <x:c r="T1" s="20" t="str">
+        <x:v>program_id</x:v>
+      </x:c>
+      <x:c r="U1" s="31" t="str">
+        <x:v>is_innate</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="11" t="str">
@@ -516,6 +679,12 @@
       </x:c>
       <x:c r="S2" s="11" t="str">
         <x:v>string</x:v>
+      </x:c>
+      <x:c r="T2" s="22" t="str">
+        <x:v>battle.MachineGunnerProgramId</x:v>
+      </x:c>
+      <x:c r="U2" s="35" t="str">
+        <x:v>bool</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
@@ -540,6 +709,8 @@
       <x:c r="Q3" s="12"/>
       <x:c r="R3" s="12"/>
       <x:c r="S3" s="12"/>
+      <x:c r="T3" s="24"/>
+      <x:c r="U3"/>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="14" t="str">
@@ -598,6 +769,12 @@
       </x:c>
       <x:c r="S4" s="14" t="str">
         <x:v>Unique card illustration key</x:v>
+      </x:c>
+      <x:c r="T4" s="26" t="str">
+        <x:v>Machine gunner card program</x:v>
+      </x:c>
+      <x:c r="U4" s="39" t="str">
+        <x:v>Whether the card is innate</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
@@ -656,6 +833,12 @@
       <x:c r="S5" s="12" t="str">
         <x:v>card_art_strength</x:v>
       </x:c>
+      <x:c r="T5" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U5" s="43" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="12"/>
@@ -713,6 +896,12 @@
       <x:c r="S6" s="12" t="str">
         <x:v>card_art_strike</x:v>
       </x:c>
+      <x:c r="T6" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U6" s="43" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="12"/>
@@ -770,6 +959,12 @@
       <x:c r="S7" s="12" t="str">
         <x:v>card_art_defend</x:v>
       </x:c>
+      <x:c r="T7" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U7" s="43" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="12"/>
@@ -827,6 +1022,12 @@
       <x:c r="S8" s="12" t="str">
         <x:v>card_art_bash</x:v>
       </x:c>
+      <x:c r="T8" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U8" s="43" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="16"/>
@@ -882,6 +1083,12 @@
       <x:c r="S9" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T9" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U9" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="16"/>
@@ -937,6 +1144,12 @@
       <x:c r="S10" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T10" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U10" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="16"/>
@@ -992,6 +1205,12 @@
       <x:c r="S11" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T11" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U11" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="16"/>
@@ -1047,6 +1266,12 @@
       <x:c r="S12" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T12" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U12" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="16"/>
@@ -1096,11 +1321,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q13" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R13" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R13" s="16" t="str">
+        <x:v>damage:4016</x:v>
+      </x:c>
       <x:c r="S13" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T13" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U13" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -1157,6 +1390,12 @@
       <x:c r="S14" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T14" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U14" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
       <x:c r="A15" s="16"/>
@@ -1212,6 +1451,12 @@
       <x:c r="S15" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T15" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U15" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
       <x:c r="A16" s="16"/>
@@ -1261,11 +1506,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q16" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R16" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R16" s="16" t="str">
+        <x:v>triggeredPlay:4018</x:v>
+      </x:c>
       <x:c r="S16" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T16" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U16" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="22" customHeight="1">
@@ -1322,6 +1575,12 @@
       <x:c r="S17" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T17" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U17" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
       <x:c r="A18" s="16"/>
@@ -1377,6 +1636,12 @@
       <x:c r="S18" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T18" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U18" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
       <x:c r="A19" s="16"/>
@@ -1432,6 +1697,12 @@
       <x:c r="S19" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T19" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U19" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" s="16"/>
@@ -1487,6 +1758,12 @@
       <x:c r="S20" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T20" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U20" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" s="16"/>
@@ -1536,11 +1813,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q21" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R21" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R21" s="16" t="str">
+        <x:v>damage:4009,cards:4010</x:v>
+      </x:c>
       <x:c r="S21" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T21" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U21" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
@@ -1597,6 +1882,12 @@
       <x:c r="S22" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T22" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U22" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
       <x:c r="A23" s="16"/>
@@ -1646,11 +1937,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q23" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R23" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R23" s="16" t="str">
+        <x:v>block:4011,cards:4010</x:v>
+      </x:c>
       <x:c r="S23" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T23" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U23" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
@@ -1701,11 +2000,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q24" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R24" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R24" s="16" t="str">
+        <x:v>damage:4015,damageRepeat1:4015,damageRepeat2:4015</x:v>
+      </x:c>
       <x:c r="S24" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T24" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U24" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="22" customHeight="1">
@@ -1762,6 +2069,12 @@
       <x:c r="S25" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T25" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U25" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
       <x:c r="A26" s="16"/>
@@ -1819,6 +2132,12 @@
       <x:c r="S26" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T26" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U26" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
       <x:c r="A27" s="16"/>
@@ -1874,6 +2193,12 @@
       <x:c r="S27" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T27" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U27" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
       <x:c r="A28" s="16"/>
@@ -1923,11 +2248,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q28" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R28" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R28" s="16" t="str">
+        <x:v>damage:4008,damageRepeat:4008</x:v>
+      </x:c>
       <x:c r="S28" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T28" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U28" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="22" customHeight="1">
@@ -1984,6 +2317,12 @@
       <x:c r="S29" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T29" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U29" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
       <x:c r="A30" s="16"/>
@@ -2039,6 +2378,12 @@
       <x:c r="S30" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T30" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U30" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" s="16"/>
@@ -2088,11 +2433,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q31" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R31" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R31" s="16" t="str">
+        <x:v>damage:4007</x:v>
+      </x:c>
       <x:c r="S31" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T31" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U31" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
@@ -2149,6 +2502,12 @@
       <x:c r="S32" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T32" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U32" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" s="16"/>
@@ -2198,11 +2557,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q33" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R33" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R33" s="16" t="str">
+        <x:v>exhaustCards:4012,cards:4013</x:v>
+      </x:c>
       <x:c r="S33" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T33" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U33" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
@@ -2259,6 +2626,12 @@
       <x:c r="S34" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T34" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U34" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="22" customHeight="1">
       <x:c r="A35" s="16"/>
@@ -2314,6 +2687,12 @@
       <x:c r="S35" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T35" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U35" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="16"/>
@@ -2369,6 +2748,12 @@
       <x:c r="S36" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T36" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U36" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="22" customHeight="1">
       <x:c r="A37" s="16"/>
@@ -2424,6 +2809,12 @@
       <x:c r="S37" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T37" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U37" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="22" customHeight="1">
       <x:c r="A38" s="16"/>
@@ -2479,6 +2870,12 @@
       <x:c r="S38" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T38" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U38" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="22" customHeight="1">
       <x:c r="A39" s="16"/>
@@ -2534,6 +2931,12 @@
       <x:c r="S39" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T39" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U39" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="22" customHeight="1">
       <x:c r="A40" s="16"/>
@@ -2589,6 +2992,12 @@
       <x:c r="S40" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T40" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U40" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="22" customHeight="1">
       <x:c r="A41" s="16"/>
@@ -2644,6 +3053,12 @@
       <x:c r="S41" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T41" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U41" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="22" customHeight="1">
       <x:c r="A42" s="16"/>
@@ -2699,6 +3114,12 @@
       <x:c r="S42" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T42" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U42" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="22" customHeight="1">
       <x:c r="A43" s="16"/>
@@ -2754,6 +3175,12 @@
       <x:c r="S43" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T43" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U43" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="22" customHeight="1">
       <x:c r="A44" s="16"/>
@@ -2809,6 +3236,12 @@
       <x:c r="S44" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T44" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U44" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="22" customHeight="1">
       <x:c r="A45" s="16"/>
@@ -2864,6 +3297,12 @@
       <x:c r="S45" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T45" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U45" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="22" customHeight="1">
       <x:c r="A46" s="16"/>
@@ -2919,6 +3358,12 @@
       <x:c r="S46" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T46" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U46" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="22" customHeight="1">
       <x:c r="A47" s="16"/>
@@ -2974,6 +3419,12 @@
       <x:c r="S47" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T47" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U47" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="22" customHeight="1">
       <x:c r="A48" s="16"/>
@@ -3029,6 +3480,12 @@
       <x:c r="S48" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T48" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U48" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="22" customHeight="1">
       <x:c r="A49" s="16"/>
@@ -3084,6 +3541,12 @@
       <x:c r="S49" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T49" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U49" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="22" customHeight="1">
       <x:c r="A50" s="16"/>
@@ -3139,6 +3602,12 @@
       <x:c r="S50" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T50" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U50" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="22" customHeight="1">
       <x:c r="A51" s="16"/>
@@ -3194,6 +3663,12 @@
       <x:c r="S51" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T51" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U51" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="22" customHeight="1">
       <x:c r="A52" s="16"/>
@@ -3249,6 +3724,12 @@
       <x:c r="S52" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T52" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U52" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="22" customHeight="1">
       <x:c r="A53" s="16"/>
@@ -3304,6 +3785,12 @@
       <x:c r="S53" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T53" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U53" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
       <x:c r="A54" s="16"/>
@@ -3359,6 +3846,12 @@
       <x:c r="S54" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T54" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U54" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="22" customHeight="1">
       <x:c r="A55" s="16"/>
@@ -3414,6 +3907,12 @@
       <x:c r="S55" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T55" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U55" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="22" customHeight="1">
       <x:c r="A56" s="16"/>
@@ -3469,6 +3968,12 @@
       <x:c r="S56" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T56" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U56" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="22" customHeight="1">
       <x:c r="A57" s="16"/>
@@ -3524,6 +4029,12 @@
       <x:c r="S57" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T57" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U57" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="22" customHeight="1">
       <x:c r="A58" s="16"/>
@@ -3579,6 +4090,12 @@
       <x:c r="S58" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T58" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U58" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
       <x:c r="A59" s="16"/>
@@ -3634,6 +4151,12 @@
       <x:c r="S59" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T59" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U59" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="22" customHeight="1">
       <x:c r="A60" s="16"/>
@@ -3689,6 +4212,12 @@
       <x:c r="S60" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T60" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U60" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="22" customHeight="1">
       <x:c r="A61" s="16"/>
@@ -3744,6 +4273,12 @@
       <x:c r="S61" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T61" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U61" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="22" customHeight="1">
       <x:c r="A62" s="16"/>
@@ -3799,6 +4334,12 @@
       <x:c r="S62" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T62" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U62" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="22" customHeight="1">
       <x:c r="A63" s="16"/>
@@ -3854,6 +4395,12 @@
       <x:c r="S63" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T63" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U63" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="22" customHeight="1">
       <x:c r="A64" s="16"/>
@@ -3909,6 +4456,12 @@
       <x:c r="S64" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T64" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U64" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="22" customHeight="1">
       <x:c r="A65" s="16"/>
@@ -3958,11 +4511,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q65" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R65" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R65" s="16" t="str">
+        <x:v>retention:4017</x:v>
+      </x:c>
       <x:c r="S65" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T65" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U65" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="22" customHeight="1">
@@ -4019,6 +4580,12 @@
       <x:c r="S66" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T66" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U66" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="22" customHeight="1">
       <x:c r="A67" s="16"/>
@@ -4074,6 +4641,12 @@
       <x:c r="S67" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T67" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U67" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="22" customHeight="1">
       <x:c r="A68" s="16"/>
@@ -4129,6 +4702,12 @@
       <x:c r="S68" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T68" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U68" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="22" customHeight="1">
       <x:c r="A69" s="16"/>
@@ -4184,6 +4763,12 @@
       <x:c r="S69" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T69" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U69" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="22" customHeight="1">
       <x:c r="A70" s="16"/>
@@ -4239,6 +4824,12 @@
       <x:c r="S70" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T70" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U70" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="22" customHeight="1">
       <x:c r="A71" s="16"/>
@@ -4294,6 +4885,12 @@
       <x:c r="S71" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T71" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U71" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="22" customHeight="1">
       <x:c r="A72" s="16"/>
@@ -4349,6 +4946,12 @@
       <x:c r="S72" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T72" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U72" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="22" customHeight="1">
       <x:c r="A73" s="16"/>
@@ -4404,6 +5007,12 @@
       <x:c r="S73" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T73" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U73" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="22" customHeight="1">
       <x:c r="A74" s="16"/>
@@ -4459,6 +5068,12 @@
       <x:c r="S74" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T74" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U74" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="22" customHeight="1">
       <x:c r="A75" s="16"/>
@@ -4514,6 +5129,12 @@
       <x:c r="S75" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T75" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U75" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="22" customHeight="1">
       <x:c r="A76" s="16"/>
@@ -4569,6 +5190,12 @@
       <x:c r="S76" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T76" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U76" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="22" customHeight="1">
       <x:c r="A77" s="16"/>
@@ -4618,11 +5245,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q77" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R77" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R77" s="16" t="str">
+        <x:v>triggerDamage:4019</x:v>
+      </x:c>
       <x:c r="S77" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T77" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U77" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="22" customHeight="1">
@@ -4679,6 +5314,12 @@
       <x:c r="S78" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T78" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U78" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="22" customHeight="1">
       <x:c r="A79" s="16"/>
@@ -4728,11 +5369,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q79" s="16" t="str">
-        <x:v>CatalogOnly</x:v>
-      </x:c>
-      <x:c r="R79" s="16" t="str"/>
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R79" s="16" t="str">
+        <x:v>heal:4014</x:v>
+      </x:c>
       <x:c r="S79" s="16" t="str">
         <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T79" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U79" s="47" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="22" customHeight="1">
@@ -4789,6 +5438,12 @@
       <x:c r="S80" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T80" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U80" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="22" customHeight="1">
       <x:c r="A81" s="16"/>
@@ -4844,6 +5499,12 @@
       <x:c r="S81" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T81" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U81" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="22" customHeight="1">
       <x:c r="A82" s="16"/>
@@ -4899,6 +5560,12 @@
       <x:c r="S82" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T82" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U82" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="22" customHeight="1">
       <x:c r="A83" s="16"/>
@@ -4954,6 +5621,12 @@
       <x:c r="S83" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T83" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U83" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="22" customHeight="1">
       <x:c r="A84" s="16"/>
@@ -5009,6 +5682,12 @@
       <x:c r="S84" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T84" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U84" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="22" customHeight="1">
       <x:c r="A85" s="16"/>
@@ -5064,6 +5743,12 @@
       <x:c r="S85" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T85" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U85" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="22" customHeight="1">
       <x:c r="A86" s="16"/>
@@ -5119,6 +5804,12 @@
       <x:c r="S86" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T86" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U86" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="22" customHeight="1">
       <x:c r="A87" s="16"/>
@@ -5174,6 +5865,12 @@
       <x:c r="S87" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T87" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U87" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="22" customHeight="1">
       <x:c r="A88" s="16"/>
@@ -5229,6 +5926,12 @@
       <x:c r="S88" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T88" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U88" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="22" customHeight="1">
       <x:c r="A89" s="16"/>
@@ -5284,6 +5987,12 @@
       <x:c r="S89" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T89" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U89" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="22" customHeight="1">
       <x:c r="A90" s="16"/>
@@ -5339,6 +6048,5014 @@
       <x:c r="S90" s="16" t="str">
         <x:v>art_placeholder</x:v>
       </x:c>
+      <x:c r="T90" s="27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="U90" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91"/>
+      <x:c r="B91" t="n">
+        <x:v>3201</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>MARINE_SHOOT</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E91" t="str">
+        <x:v>battle.card.marine.shoot.name</x:v>
+      </x:c>
+      <x:c r="F91" t="str">
+        <x:v>battle.card.marine.shoot.description</x:v>
+      </x:c>
+      <x:c r="G91" t="str">
+        <x:v>battle.card.marine.shoot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H91" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I91" t="str">
+        <x:v>Basic</x:v>
+      </x:c>
+      <x:c r="J91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K91" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M91" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N91" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O91" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P91" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q91" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R91"/>
+      <x:c r="S91" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T91" s="27" t="str">
+        <x:v>Shoot</x:v>
+      </x:c>
+      <x:c r="U91" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92"/>
+      <x:c r="B92" t="n">
+        <x:v>3202</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>MARINE_ELBOW</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E92" t="str">
+        <x:v>battle.card.marine.elbow.name</x:v>
+      </x:c>
+      <x:c r="F92" t="str">
+        <x:v>battle.card.marine.elbow.description</x:v>
+      </x:c>
+      <x:c r="G92" t="str">
+        <x:v>battle.card.marine.elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H92" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I92" t="str">
+        <x:v>Basic</x:v>
+      </x:c>
+      <x:c r="J92" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K92" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L92" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M92" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N92" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O92" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P92" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q92" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R92"/>
+      <x:c r="S92" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T92" s="27" t="str">
+        <x:v>Elbow</x:v>
+      </x:c>
+      <x:c r="U92" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93"/>
+      <x:c r="B93" t="n">
+        <x:v>3203</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>MARINE_BLOCK</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E93" t="str">
+        <x:v>battle.card.marine.block.name</x:v>
+      </x:c>
+      <x:c r="F93" t="str">
+        <x:v>battle.card.marine.block.description</x:v>
+      </x:c>
+      <x:c r="G93" t="str">
+        <x:v>battle.card.marine.block.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H93" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I93" t="str">
+        <x:v>Basic</x:v>
+      </x:c>
+      <x:c r="J93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K93" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M93" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N93" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O93" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P93" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q93" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R93"/>
+      <x:c r="S93" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T93" s="27" t="str">
+        <x:v>Block</x:v>
+      </x:c>
+      <x:c r="U93" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94"/>
+      <x:c r="B94" t="n">
+        <x:v>3204</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>MARINE_RELOAD</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>battle.card.marine.reload.name</x:v>
+      </x:c>
+      <x:c r="F94" t="str">
+        <x:v>battle.card.marine.reload.description</x:v>
+      </x:c>
+      <x:c r="G94" t="str">
+        <x:v>battle.card.marine.reload.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H94" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I94" t="str">
+        <x:v>Basic</x:v>
+      </x:c>
+      <x:c r="J94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K94" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M94" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N94" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O94" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P94" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q94" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R94"/>
+      <x:c r="S94" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T94" s="27" t="str">
+        <x:v>Reload</x:v>
+      </x:c>
+      <x:c r="U94" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95"/>
+      <x:c r="B95" t="n">
+        <x:v>3205</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>MARINE_STIM</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E95" t="str">
+        <x:v>battle.card.marine.stim.name</x:v>
+      </x:c>
+      <x:c r="F95" t="str">
+        <x:v>battle.card.marine.stim.description</x:v>
+      </x:c>
+      <x:c r="G95" t="str">
+        <x:v>battle.card.marine.stim.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H95" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I95" t="str">
+        <x:v>Basic</x:v>
+      </x:c>
+      <x:c r="J95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K95" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M95" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N95" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O95" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P95" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q95" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R95"/>
+      <x:c r="S95" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T95" s="27" t="str">
+        <x:v>Stim</x:v>
+      </x:c>
+      <x:c r="U95" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96"/>
+      <x:c r="B96" t="n">
+        <x:v>3206</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>MARINE_CORE_EXPANSION</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E96" t="str">
+        <x:v>battle.card.marine.core_expansion.name</x:v>
+      </x:c>
+      <x:c r="F96" t="str">
+        <x:v>battle.card.marine.core_expansion.description</x:v>
+      </x:c>
+      <x:c r="G96" t="str">
+        <x:v>battle.card.marine.core_expansion.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H96" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I96" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J96" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K96" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L96" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M96" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N96" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O96" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P96" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q96" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R96"/>
+      <x:c r="S96" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T96" s="27" t="str">
+        <x:v>CoreExpansion</x:v>
+      </x:c>
+      <x:c r="U96" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97"/>
+      <x:c r="B97" t="n">
+        <x:v>3207</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>MARINE_OUTPUT_ADJUST</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>battle.card.marine.output_adjust.name</x:v>
+      </x:c>
+      <x:c r="F97" t="str">
+        <x:v>battle.card.marine.output_adjust.description</x:v>
+      </x:c>
+      <x:c r="G97" t="str">
+        <x:v>battle.card.marine.output_adjust.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H97" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I97" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K97" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M97" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N97" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O97" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P97" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q97" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R97"/>
+      <x:c r="S97" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T97" s="27" t="str">
+        <x:v>OutputAdjust</x:v>
+      </x:c>
+      <x:c r="U97" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98"/>
+      <x:c r="B98" t="n">
+        <x:v>3208</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>MARINE_BLAST_SHIELD</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>battle.card.marine.blast_shield.name</x:v>
+      </x:c>
+      <x:c r="F98" t="str">
+        <x:v>battle.card.marine.blast_shield.description</x:v>
+      </x:c>
+      <x:c r="G98" t="str">
+        <x:v>battle.card.marine.blast_shield.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H98" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M98" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N98" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O98" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P98" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q98" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R98"/>
+      <x:c r="S98" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T98" s="27" t="str">
+        <x:v>BlastShield</x:v>
+      </x:c>
+      <x:c r="U98" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99"/>
+      <x:c r="B99" t="n">
+        <x:v>3209</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>MARINE_MAG_EXPANSION</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>battle.card.marine.mag_expansion.name</x:v>
+      </x:c>
+      <x:c r="F99" t="str">
+        <x:v>battle.card.marine.mag_expansion.description</x:v>
+      </x:c>
+      <x:c r="G99" t="str">
+        <x:v>battle.card.marine.mag_expansion.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H99" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I99" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K99" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M99" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N99" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O99" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P99" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q99" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R99"/>
+      <x:c r="S99" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T99" s="27" t="str">
+        <x:v>MagExpansion</x:v>
+      </x:c>
+      <x:c r="U99" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100"/>
+      <x:c r="B100" t="n">
+        <x:v>3210</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>MARINE_INCENDIARY_AMMO</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>battle.card.marine.incendiary_ammo.name</x:v>
+      </x:c>
+      <x:c r="F100" t="str">
+        <x:v>battle.card.marine.incendiary_ammo.description</x:v>
+      </x:c>
+      <x:c r="G100" t="str">
+        <x:v>battle.card.marine.incendiary_ammo.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H100" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I100" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K100" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M100" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N100" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O100" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P100" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q100" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R100"/>
+      <x:c r="S100" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T100" s="27" t="str">
+        <x:v>IncendiaryAmmo</x:v>
+      </x:c>
+      <x:c r="U100" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101"/>
+      <x:c r="B101" t="n">
+        <x:v>3211</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>MARINE_SMOKE_PERSIST</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>battle.card.marine.smoke_persist.name</x:v>
+      </x:c>
+      <x:c r="F101" t="str">
+        <x:v>battle.card.marine.smoke_persist.description</x:v>
+      </x:c>
+      <x:c r="G101" t="str">
+        <x:v>battle.card.marine.smoke_persist.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H101" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I101" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K101" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M101" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N101" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O101" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P101" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q101" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R101"/>
+      <x:c r="S101" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T101" s="27" t="str">
+        <x:v>SmokePersist</x:v>
+      </x:c>
+      <x:c r="U101" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102"/>
+      <x:c r="B102" t="n">
+        <x:v>3212</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>MARINE_KUNGFU_MECH</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>battle.card.marine.kungfu_mech.name</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>battle.card.marine.kungfu_mech.description</x:v>
+      </x:c>
+      <x:c r="G102" t="str">
+        <x:v>battle.card.marine.kungfu_mech.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H102" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K102" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M102" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N102" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O102" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P102" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q102" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R102"/>
+      <x:c r="S102" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T102" s="27" t="str">
+        <x:v>KungfuMech</x:v>
+      </x:c>
+      <x:c r="U102" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103"/>
+      <x:c r="B103" t="n">
+        <x:v>3213</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>MARINE_OVERLOAD</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>battle.card.marine.overload.name</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>battle.card.marine.overload.description</x:v>
+      </x:c>
+      <x:c r="G103" t="str">
+        <x:v>battle.card.marine.overload.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J103" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L103" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M103" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N103" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O103" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P103" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q103" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R103"/>
+      <x:c r="S103" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T103" s="27" t="str">
+        <x:v>Overload</x:v>
+      </x:c>
+      <x:c r="U103" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104"/>
+      <x:c r="B104" t="n">
+        <x:v>3214</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>MARINE_TUMBLE_RELOAD</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>battle.card.marine.tumble_reload.name</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>battle.card.marine.tumble_reload.description</x:v>
+      </x:c>
+      <x:c r="G104" t="str">
+        <x:v>battle.card.marine.tumble_reload.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M104" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N104" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O104" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P104" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q104" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R104"/>
+      <x:c r="S104" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T104" s="27" t="str">
+        <x:v>TumbleReload</x:v>
+      </x:c>
+      <x:c r="U104" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105"/>
+      <x:c r="B105" t="n">
+        <x:v>3215</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>MARINE_STUN_GRENADE</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>battle.card.marine.stun_grenade.name</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>battle.card.marine.stun_grenade.description</x:v>
+      </x:c>
+      <x:c r="G105" t="str">
+        <x:v>battle.card.marine.stun_grenade.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H105" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J105" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L105" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M105" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N105" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O105" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P105" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q105" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R105"/>
+      <x:c r="S105" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T105" s="27" t="str">
+        <x:v>StunGrenade</x:v>
+      </x:c>
+      <x:c r="U105" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106"/>
+      <x:c r="B106" t="n">
+        <x:v>3216</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>MARINE_RETREAT</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>battle.card.marine.retreat.name</x:v>
+      </x:c>
+      <x:c r="F106" t="str">
+        <x:v>battle.card.marine.retreat.description</x:v>
+      </x:c>
+      <x:c r="G106" t="str">
+        <x:v>battle.card.marine.retreat.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H106" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J106" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L106" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M106" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N106" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O106" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P106" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q106" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R106"/>
+      <x:c r="S106" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T106" s="27" t="str">
+        <x:v>Retreat</x:v>
+      </x:c>
+      <x:c r="U106" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107"/>
+      <x:c r="B107" t="n">
+        <x:v>3217</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>MARINE_GAS_PUMP</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E107" t="str">
+        <x:v>battle.card.marine.gas_pump.name</x:v>
+      </x:c>
+      <x:c r="F107" t="str">
+        <x:v>battle.card.marine.gas_pump.description</x:v>
+      </x:c>
+      <x:c r="G107" t="str">
+        <x:v>battle.card.marine.gas_pump.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H107" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I107" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K107" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M107" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N107" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O107" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P107" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q107" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R107"/>
+      <x:c r="S107" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T107" s="27" t="str">
+        <x:v>GasPump</x:v>
+      </x:c>
+      <x:c r="U107" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108"/>
+      <x:c r="B108" t="n">
+        <x:v>3218</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>MARINE_NAPALM</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E108" t="str">
+        <x:v>battle.card.marine.napalm.name</x:v>
+      </x:c>
+      <x:c r="F108" t="str">
+        <x:v>battle.card.marine.napalm.description</x:v>
+      </x:c>
+      <x:c r="G108" t="str">
+        <x:v>battle.card.marine.napalm.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H108" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I108" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J108" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K108" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L108" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M108" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N108" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O108" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P108" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q108" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R108"/>
+      <x:c r="S108" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T108" s="27" t="str">
+        <x:v>Napalm</x:v>
+      </x:c>
+      <x:c r="U108" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109"/>
+      <x:c r="B109" t="n">
+        <x:v>3219</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>MARINE_MOLOTOV</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E109" t="str">
+        <x:v>battle.card.marine.molotov.name</x:v>
+      </x:c>
+      <x:c r="F109" t="str">
+        <x:v>battle.card.marine.molotov.description</x:v>
+      </x:c>
+      <x:c r="G109" t="str">
+        <x:v>battle.card.marine.molotov.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H109" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I109" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J109" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K109" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L109" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M109" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N109" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O109" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P109" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q109" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R109"/>
+      <x:c r="S109" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T109" s="27" t="str">
+        <x:v>Molotov</x:v>
+      </x:c>
+      <x:c r="U109" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110"/>
+      <x:c r="B110" t="n">
+        <x:v>3220</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>MARINE_HOLD_LINE</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E110" t="str">
+        <x:v>battle.card.marine.hold_line.name</x:v>
+      </x:c>
+      <x:c r="F110" t="str">
+        <x:v>battle.card.marine.hold_line.description</x:v>
+      </x:c>
+      <x:c r="G110" t="str">
+        <x:v>battle.card.marine.hold_line.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H110" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I110" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K110" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="L110" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M110" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N110" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O110" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P110" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q110" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R110"/>
+      <x:c r="S110" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T110" s="27" t="str">
+        <x:v>HoldLine</x:v>
+      </x:c>
+      <x:c r="U110" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111"/>
+      <x:c r="B111" t="n">
+        <x:v>3221</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>MARINE_SMOKE_BOMB</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E111" t="str">
+        <x:v>battle.card.marine.smoke_bomb.name</x:v>
+      </x:c>
+      <x:c r="F111" t="str">
+        <x:v>battle.card.marine.smoke_bomb.description</x:v>
+      </x:c>
+      <x:c r="G111" t="str">
+        <x:v>battle.card.marine.smoke_bomb.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H111" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I111" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J111" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K111" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L111" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M111" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N111" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O111" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P111" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q111" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R111"/>
+      <x:c r="S111" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T111" s="27" t="str">
+        <x:v>SmokeBomb</x:v>
+      </x:c>
+      <x:c r="U111" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112"/>
+      <x:c r="B112" t="n">
+        <x:v>3222</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>MARINE_INCOMPLETE_COMBUSTION</x:v>
+      </x:c>
+      <x:c r="D112" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E112" t="str">
+        <x:v>battle.card.marine.incomplete_combustion.name</x:v>
+      </x:c>
+      <x:c r="F112" t="str">
+        <x:v>battle.card.marine.incomplete_combustion.description</x:v>
+      </x:c>
+      <x:c r="G112" t="str">
+        <x:v>battle.card.marine.incomplete_combustion.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H112" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I112" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J112" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K112" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L112" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M112" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N112" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="O112" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="P112" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q112" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R112"/>
+      <x:c r="S112" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T112" s="27" t="str">
+        <x:v>IncompleteCombustion</x:v>
+      </x:c>
+      <x:c r="U112" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113"/>
+      <x:c r="B113" t="n">
+        <x:v>3223</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>MARINE_KNOCKBACK_SHOT</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>battle.card.marine.knockback_shot.name</x:v>
+      </x:c>
+      <x:c r="F113" t="str">
+        <x:v>battle.card.marine.knockback_shot.description</x:v>
+      </x:c>
+      <x:c r="G113" t="str">
+        <x:v>battle.card.marine.knockback_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H113" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K113" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L113" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M113" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N113" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O113" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P113" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q113" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R113"/>
+      <x:c r="S113" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T113" s="27" t="str">
+        <x:v>KnockbackShot</x:v>
+      </x:c>
+      <x:c r="U113" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114"/>
+      <x:c r="B114" t="n">
+        <x:v>3224</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>MARINE_SPRAY</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>battle.card.marine.spray.name</x:v>
+      </x:c>
+      <x:c r="F114" t="str">
+        <x:v>battle.card.marine.spray.description</x:v>
+      </x:c>
+      <x:c r="G114" t="str">
+        <x:v>battle.card.marine.spray.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H114" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K114" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L114" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M114" t="str">
+        <x:v>RandomEnemy</x:v>
+      </x:c>
+      <x:c r="N114" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O114" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P114" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q114" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R114"/>
+      <x:c r="S114" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T114" s="27" t="str">
+        <x:v>Spray</x:v>
+      </x:c>
+      <x:c r="U114" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115"/>
+      <x:c r="B115" t="n">
+        <x:v>3225</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>MARINE_BAYONET_PARRY</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>battle.card.marine.bayonet_parry.name</x:v>
+      </x:c>
+      <x:c r="F115" t="str">
+        <x:v>battle.card.marine.bayonet_parry.description</x:v>
+      </x:c>
+      <x:c r="G115" t="str">
+        <x:v>battle.card.marine.bayonet_parry.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H115" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J115" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L115" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M115" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N115" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O115" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P115" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q115" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R115"/>
+      <x:c r="S115" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T115" s="27" t="str">
+        <x:v>BayonetParry</x:v>
+      </x:c>
+      <x:c r="U115" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116"/>
+      <x:c r="B116" t="n">
+        <x:v>3226</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>MARINE_WILD_RAMPAGE</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>battle.card.marine.wild_rampage.name</x:v>
+      </x:c>
+      <x:c r="F116" t="str">
+        <x:v>battle.card.marine.wild_rampage.description</x:v>
+      </x:c>
+      <x:c r="G116" t="str">
+        <x:v>battle.card.marine.wild_rampage.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H116" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="L116" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M116" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N116" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O116" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P116" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q116" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R116"/>
+      <x:c r="S116" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T116" s="27" t="str">
+        <x:v>WildRampage</x:v>
+      </x:c>
+      <x:c r="U116" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117"/>
+      <x:c r="B117" t="n">
+        <x:v>3227</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>MARINE_QUICK_ELBOW</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>battle.card.marine.quick_elbow.name</x:v>
+      </x:c>
+      <x:c r="F117" t="str">
+        <x:v>battle.card.marine.quick_elbow.description</x:v>
+      </x:c>
+      <x:c r="G117" t="str">
+        <x:v>battle.card.marine.quick_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H117" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L117" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M117" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N117" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O117" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P117" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q117" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R117"/>
+      <x:c r="S117" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T117" s="27" t="str">
+        <x:v>QuickElbow</x:v>
+      </x:c>
+      <x:c r="U117" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118"/>
+      <x:c r="B118" t="n">
+        <x:v>3228</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>MARINE_KIDNEY_SHOT</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>battle.card.marine.kidney_shot.name</x:v>
+      </x:c>
+      <x:c r="F118" t="str">
+        <x:v>battle.card.marine.kidney_shot.description</x:v>
+      </x:c>
+      <x:c r="G118" t="str">
+        <x:v>battle.card.marine.kidney_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H118" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J118" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L118" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M118" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N118" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O118" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P118" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q118" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R118"/>
+      <x:c r="S118" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T118" s="27" t="str">
+        <x:v>KidneyShot</x:v>
+      </x:c>
+      <x:c r="U118" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119"/>
+      <x:c r="B119" t="n">
+        <x:v>3229</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>MARINE_PAINFUL_ELBOW</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>battle.card.marine.painful_elbow.name</x:v>
+      </x:c>
+      <x:c r="F119" t="str">
+        <x:v>battle.card.marine.painful_elbow.description</x:v>
+      </x:c>
+      <x:c r="G119" t="str">
+        <x:v>battle.card.marine.painful_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H119" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J119" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L119" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M119" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N119" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O119" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P119" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q119" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R119"/>
+      <x:c r="S119" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T119" s="27" t="str">
+        <x:v>PainfulElbow</x:v>
+      </x:c>
+      <x:c r="U119" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120"/>
+      <x:c r="B120" t="n">
+        <x:v>3230</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>MARINE_HEAVY_ELBOW</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>battle.card.marine.heavy_elbow.name</x:v>
+      </x:c>
+      <x:c r="F120" t="str">
+        <x:v>battle.card.marine.heavy_elbow.description</x:v>
+      </x:c>
+      <x:c r="G120" t="str">
+        <x:v>battle.card.marine.heavy_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H120" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J120" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K120" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L120" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M120" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N120" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O120" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P120" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q120" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R120"/>
+      <x:c r="S120" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T120" s="27" t="str">
+        <x:v>HeavyElbow</x:v>
+      </x:c>
+      <x:c r="U120" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121"/>
+      <x:c r="B121" t="n">
+        <x:v>3231</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>MARINE_FIELD_SURGERY</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>battle.card.marine.field_surgery.name</x:v>
+      </x:c>
+      <x:c r="F121" t="str">
+        <x:v>battle.card.marine.field_surgery.description</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>battle.card.marine.field_surgery.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J121" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L121" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M121" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N121" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="O121" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="P121" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q121" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R121"/>
+      <x:c r="S121" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T121" s="27" t="str">
+        <x:v>FieldSurgery</x:v>
+      </x:c>
+      <x:c r="U121" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122"/>
+      <x:c r="B122" t="n">
+        <x:v>3232</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>MARINE_HURRICANE_ELBOW</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>battle.card.marine.hurricane_elbow.name</x:v>
+      </x:c>
+      <x:c r="F122" t="str">
+        <x:v>battle.card.marine.hurricane_elbow.description</x:v>
+      </x:c>
+      <x:c r="G122" t="str">
+        <x:v>battle.card.marine.hurricane_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H122" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K122" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="L122" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M122" t="str">
+        <x:v>RandomEnemy</x:v>
+      </x:c>
+      <x:c r="N122" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O122" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P122" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q122" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R122"/>
+      <x:c r="S122" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T122" s="27" t="str">
+        <x:v>HurricaneElbow</x:v>
+      </x:c>
+      <x:c r="U122" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123"/>
+      <x:c r="B123" t="n">
+        <x:v>3233</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>MARINE_PRECISION_SHOT</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>battle.card.marine.precision_shot.name</x:v>
+      </x:c>
+      <x:c r="F123" t="str">
+        <x:v>battle.card.marine.precision_shot.description</x:v>
+      </x:c>
+      <x:c r="G123" t="str">
+        <x:v>battle.card.marine.precision_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H123" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I123" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J123" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K123" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L123" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M123" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N123" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O123" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P123" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q123" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R123"/>
+      <x:c r="S123" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T123" s="27" t="str">
+        <x:v>PrecisionShot</x:v>
+      </x:c>
+      <x:c r="U123" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124"/>
+      <x:c r="B124" t="n">
+        <x:v>3234</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>MARINE_TACTICAL_ADVANCE</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E124" t="str">
+        <x:v>battle.card.marine.tactical_advance.name</x:v>
+      </x:c>
+      <x:c r="F124" t="str">
+        <x:v>battle.card.marine.tactical_advance.description</x:v>
+      </x:c>
+      <x:c r="G124" t="str">
+        <x:v>battle.card.marine.tactical_advance.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H124" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I124" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J124" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K124" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L124" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M124" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N124" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O124" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P124" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q124" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R124"/>
+      <x:c r="S124" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T124" s="27" t="str">
+        <x:v>TacticalAdvance</x:v>
+      </x:c>
+      <x:c r="U124" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125"/>
+      <x:c r="B125" t="n">
+        <x:v>3235</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>MARINE_QUICK_ROLL</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E125" t="str">
+        <x:v>battle.card.marine.quick_roll.name</x:v>
+      </x:c>
+      <x:c r="F125" t="str">
+        <x:v>battle.card.marine.quick_roll.description</x:v>
+      </x:c>
+      <x:c r="G125" t="str">
+        <x:v>battle.card.marine.quick_roll.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H125" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I125" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J125" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K125" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L125" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M125" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N125" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O125" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P125" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q125" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R125"/>
+      <x:c r="S125" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T125" s="27" t="str">
+        <x:v>QuickRoll</x:v>
+      </x:c>
+      <x:c r="U125" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126"/>
+      <x:c r="B126" t="n">
+        <x:v>3236</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>MARINE_ELECTRO_BOOST</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E126" t="str">
+        <x:v>battle.card.marine.electro_boost.name</x:v>
+      </x:c>
+      <x:c r="F126" t="str">
+        <x:v>battle.card.marine.electro_boost.description</x:v>
+      </x:c>
+      <x:c r="G126" t="str">
+        <x:v>battle.card.marine.electro_boost.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H126" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I126" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J126" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K126" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L126" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M126" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N126" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O126" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P126" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q126" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R126"/>
+      <x:c r="S126" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T126" s="27" t="str">
+        <x:v>ElectroBoost</x:v>
+      </x:c>
+      <x:c r="U126" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127"/>
+      <x:c r="B127" t="n">
+        <x:v>3237</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>MARINE_GUIDED_NUKE</x:v>
+      </x:c>
+      <x:c r="D127" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E127" t="str">
+        <x:v>battle.card.marine.guided_nuke.name</x:v>
+      </x:c>
+      <x:c r="F127" t="str">
+        <x:v>battle.card.marine.guided_nuke.description</x:v>
+      </x:c>
+      <x:c r="G127" t="str">
+        <x:v>battle.card.marine.guided_nuke.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H127" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I127" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J127" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K127" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L127" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M127" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N127" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O127" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P127" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q127" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R127"/>
+      <x:c r="S127" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T127" s="27" t="str">
+        <x:v>GuidedNuke</x:v>
+      </x:c>
+      <x:c r="U127" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128"/>
+      <x:c r="B128" t="n">
+        <x:v>3238</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>MARINE_BANSHEE_STRIKE</x:v>
+      </x:c>
+      <x:c r="D128" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E128" t="str">
+        <x:v>battle.card.marine.banshee_strike.name</x:v>
+      </x:c>
+      <x:c r="F128" t="str">
+        <x:v>battle.card.marine.banshee_strike.description</x:v>
+      </x:c>
+      <x:c r="G128" t="str">
+        <x:v>battle.card.marine.banshee_strike.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H128" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I128" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J128" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K128" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L128" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M128" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N128" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O128" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P128" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q128" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R128"/>
+      <x:c r="S128" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T128" s="27" t="str">
+        <x:v>BansheeStrike</x:v>
+      </x:c>
+      <x:c r="U128" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129"/>
+      <x:c r="B129" t="n">
+        <x:v>3239</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>MARINE_FIRE_SUPPORT</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E129" t="str">
+        <x:v>battle.card.marine.fire_support.name</x:v>
+      </x:c>
+      <x:c r="F129" t="str">
+        <x:v>battle.card.marine.fire_support.description</x:v>
+      </x:c>
+      <x:c r="G129" t="str">
+        <x:v>battle.card.marine.fire_support.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H129" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I129" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J129" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K129" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L129" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M129" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N129" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O129" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P129" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q129" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R129"/>
+      <x:c r="S129" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T129" s="27" t="str">
+        <x:v>FireSupport</x:v>
+      </x:c>
+      <x:c r="U129" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130"/>
+      <x:c r="B130" t="n">
+        <x:v>3240</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>MARINE_FIRE_BOMBARDMENT</x:v>
+      </x:c>
+      <x:c r="D130" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E130" t="str">
+        <x:v>battle.card.marine.fire_bombardment.name</x:v>
+      </x:c>
+      <x:c r="F130" t="str">
+        <x:v>battle.card.marine.fire_bombardment.description</x:v>
+      </x:c>
+      <x:c r="G130" t="str">
+        <x:v>battle.card.marine.fire_bombardment.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H130" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I130" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J130" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K130" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L130" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M130" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N130" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O130" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P130" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q130" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R130"/>
+      <x:c r="S130" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T130" s="27" t="str">
+        <x:v>FireBombardment</x:v>
+      </x:c>
+      <x:c r="U130" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131"/>
+      <x:c r="B131" t="n">
+        <x:v>3241</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>MARINE_FIVE_HUNDRED_POUNDER</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E131" t="str">
+        <x:v>battle.card.marine.five_hundred_pounder.name</x:v>
+      </x:c>
+      <x:c r="F131" t="str">
+        <x:v>battle.card.marine.five_hundred_pounder.description</x:v>
+      </x:c>
+      <x:c r="G131" t="str">
+        <x:v>battle.card.marine.five_hundred_pounder.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H131" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I131" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J131" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K131" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L131" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M131" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N131" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O131" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P131" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q131" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R131"/>
+      <x:c r="S131" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T131" s="27" t="str">
+        <x:v>FiveHundredPounder</x:v>
+      </x:c>
+      <x:c r="U131" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132"/>
+      <x:c r="B132" t="n">
+        <x:v>3242</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>MARINE_COMBO_ELBOW</x:v>
+      </x:c>
+      <x:c r="D132" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E132" t="str">
+        <x:v>battle.card.marine.combo_elbow.name</x:v>
+      </x:c>
+      <x:c r="F132" t="str">
+        <x:v>battle.card.marine.combo_elbow.description</x:v>
+      </x:c>
+      <x:c r="G132" t="str">
+        <x:v>battle.card.marine.combo_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H132" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I132" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J132" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K132" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L132" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M132" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N132" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O132" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P132" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q132" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R132"/>
+      <x:c r="S132" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T132" s="27" t="str">
+        <x:v>ComboElbow</x:v>
+      </x:c>
+      <x:c r="U132" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133"/>
+      <x:c r="B133" t="n">
+        <x:v>3243</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>MARINE_OPPORTUNISTIC_STRIKE</x:v>
+      </x:c>
+      <x:c r="D133" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E133" t="str">
+        <x:v>battle.card.marine.opportunistic_strike.name</x:v>
+      </x:c>
+      <x:c r="F133" t="str">
+        <x:v>battle.card.marine.opportunistic_strike.description</x:v>
+      </x:c>
+      <x:c r="G133" t="str">
+        <x:v>battle.card.marine.opportunistic_strike.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H133" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I133" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J133" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K133" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L133" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M133" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N133" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O133" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P133" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q133" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R133"/>
+      <x:c r="S133" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T133" s="27" t="str">
+        <x:v>OpportunisticStrike</x:v>
+      </x:c>
+      <x:c r="U133" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134"/>
+      <x:c r="B134" t="n">
+        <x:v>3244</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>MARINE_VENT_HEAT</x:v>
+      </x:c>
+      <x:c r="D134" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E134" t="str">
+        <x:v>battle.card.marine.vent_heat.name</x:v>
+      </x:c>
+      <x:c r="F134" t="str">
+        <x:v>battle.card.marine.vent_heat.description</x:v>
+      </x:c>
+      <x:c r="G134" t="str">
+        <x:v>battle.card.marine.vent_heat.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H134" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I134" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K134" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M134" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N134" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O134" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P134" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q134" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R134"/>
+      <x:c r="S134" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T134" s="27" t="str">
+        <x:v>VentHeat</x:v>
+      </x:c>
+      <x:c r="U134" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135"/>
+      <x:c r="B135" t="n">
+        <x:v>3245</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>MARINE_POWER_OVERCLOCK</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>battle.card.marine.power_overclock.name</x:v>
+      </x:c>
+      <x:c r="F135" t="str">
+        <x:v>battle.card.marine.power_overclock.description</x:v>
+      </x:c>
+      <x:c r="G135" t="str">
+        <x:v>battle.card.marine.power_overclock.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H135" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I135" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J135" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K135" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M135" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N135" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O135" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P135" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q135" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R135"/>
+      <x:c r="S135" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T135" s="27" t="str">
+        <x:v>PowerOverclock</x:v>
+      </x:c>
+      <x:c r="U135" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136"/>
+      <x:c r="B136" t="n">
+        <x:v>3246</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>MARINE_GARRISON</x:v>
+      </x:c>
+      <x:c r="D136" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E136" t="str">
+        <x:v>battle.card.marine.garrison.name</x:v>
+      </x:c>
+      <x:c r="F136" t="str">
+        <x:v>battle.card.marine.garrison.description</x:v>
+      </x:c>
+      <x:c r="G136" t="str">
+        <x:v>battle.card.marine.garrison.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H136" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I136" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J136" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K136" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L136" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M136" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N136" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O136" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P136" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q136" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R136"/>
+      <x:c r="S136" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T136" s="27" t="str">
+        <x:v>Garrison</x:v>
+      </x:c>
+      <x:c r="U136" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137"/>
+      <x:c r="B137" t="n">
+        <x:v>3247</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>MARINE_SNIPER_SHOT</x:v>
+      </x:c>
+      <x:c r="D137" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E137" t="str">
+        <x:v>battle.card.marine.sniper_shot.name</x:v>
+      </x:c>
+      <x:c r="F137" t="str">
+        <x:v>battle.card.marine.sniper_shot.description</x:v>
+      </x:c>
+      <x:c r="G137" t="str">
+        <x:v>battle.card.marine.sniper_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H137" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I137" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J137" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K137" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L137" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M137" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N137" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O137" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P137" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q137" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R137"/>
+      <x:c r="S137" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T137" s="27" t="str">
+        <x:v>SniperShot</x:v>
+      </x:c>
+      <x:c r="U137" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138"/>
+      <x:c r="B138" t="n">
+        <x:v>3248</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>MARINE_SPIKE_SHOT</x:v>
+      </x:c>
+      <x:c r="D138" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E138" t="str">
+        <x:v>battle.card.marine.spike_shot.name</x:v>
+      </x:c>
+      <x:c r="F138" t="str">
+        <x:v>battle.card.marine.spike_shot.description</x:v>
+      </x:c>
+      <x:c r="G138" t="str">
+        <x:v>battle.card.marine.spike_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H138" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I138" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K138" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M138" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N138" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O138" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P138" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q138" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R138"/>
+      <x:c r="S138" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T138" s="27" t="str">
+        <x:v>SpikeShot</x:v>
+      </x:c>
+      <x:c r="U138" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139"/>
+      <x:c r="B139" t="n">
+        <x:v>3249</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>MARINE_OPTICAL_CAMO</x:v>
+      </x:c>
+      <x:c r="D139" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E139" t="str">
+        <x:v>battle.card.marine.optical_camo.name</x:v>
+      </x:c>
+      <x:c r="F139" t="str">
+        <x:v>battle.card.marine.optical_camo.description</x:v>
+      </x:c>
+      <x:c r="G139" t="str">
+        <x:v>battle.card.marine.optical_camo.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H139" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I139" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J139" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K139" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L139" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M139" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N139" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O139" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P139" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q139" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R139"/>
+      <x:c r="S139" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T139" s="27" t="str">
+        <x:v>OpticalCamo</x:v>
+      </x:c>
+      <x:c r="U139" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140"/>
+      <x:c r="B140" t="n">
+        <x:v>3250</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>MARINE_UNSTOPPABLE</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>battle.card.marine.unstoppable.name</x:v>
+      </x:c>
+      <x:c r="F140" t="str">
+        <x:v>battle.card.marine.unstoppable.description</x:v>
+      </x:c>
+      <x:c r="G140" t="str">
+        <x:v>battle.card.marine.unstoppable.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H140" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I140" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J140" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K140" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L140" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M140" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N140" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O140" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P140" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q140" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R140"/>
+      <x:c r="S140" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T140" s="27" t="str">
+        <x:v>Unstoppable</x:v>
+      </x:c>
+      <x:c r="U140" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141"/>
+      <x:c r="B141" t="n">
+        <x:v>3251</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>MARINE_GUERRILLA_TACTICS</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>battle.card.marine.guerrilla_tactics.name</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>battle.card.marine.guerrilla_tactics.description</x:v>
+      </x:c>
+      <x:c r="G141" t="str">
+        <x:v>battle.card.marine.guerrilla_tactics.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H141" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I141" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J141" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K141" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L141" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M141" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N141" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O141" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P141" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q141" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R141"/>
+      <x:c r="S141" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T141" s="27" t="str">
+        <x:v>GuerrillaTactics</x:v>
+      </x:c>
+      <x:c r="U141" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142"/>
+      <x:c r="B142" t="n">
+        <x:v>3252</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>MARINE_EXPLOSIVE_ELBOW</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>battle.card.marine.explosive_elbow.name</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>battle.card.marine.explosive_elbow.description</x:v>
+      </x:c>
+      <x:c r="G142" t="str">
+        <x:v>battle.card.marine.explosive_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H142" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I142" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J142" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K142" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L142" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M142" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N142" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O142" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P142" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q142" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R142"/>
+      <x:c r="S142" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T142" s="27" t="str">
+        <x:v>ExplosiveElbow</x:v>
+      </x:c>
+      <x:c r="U142" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143"/>
+      <x:c r="B143" t="n">
+        <x:v>3253</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>MARINE_AGED_OIL</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>battle.card.marine.aged_oil.name</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>battle.card.marine.aged_oil.description</x:v>
+      </x:c>
+      <x:c r="G143" t="str">
+        <x:v>battle.card.marine.aged_oil.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H143" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I143" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J143" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K143" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L143" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M143" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N143" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O143" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P143" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q143" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R143"/>
+      <x:c r="S143" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T143" s="27" t="str">
+        <x:v>AgedOil</x:v>
+      </x:c>
+      <x:c r="U143" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144"/>
+      <x:c r="B144" t="n">
+        <x:v>3254</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>MARINE_BURNING_OIL</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>battle.card.marine.burning_oil.name</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>battle.card.marine.burning_oil.description</x:v>
+      </x:c>
+      <x:c r="G144" t="str">
+        <x:v>battle.card.marine.burning_oil.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H144" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I144" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J144" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K144" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L144" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M144" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N144" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O144" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P144" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q144" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R144"/>
+      <x:c r="S144" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T144" s="27" t="str">
+        <x:v>BurningOil</x:v>
+      </x:c>
+      <x:c r="U144" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145"/>
+      <x:c r="B145" t="n">
+        <x:v>3255</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>MARINE_FLAME_ELBOW</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>battle.card.marine.flame_elbow.name</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>battle.card.marine.flame_elbow.description</x:v>
+      </x:c>
+      <x:c r="G145" t="str">
+        <x:v>battle.card.marine.flame_elbow.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H145" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I145" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J145" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K145" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L145" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M145" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N145" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O145" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P145" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q145" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R145"/>
+      <x:c r="S145" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T145" s="27" t="str">
+        <x:v>FlameElbow</x:v>
+      </x:c>
+      <x:c r="U145" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146"/>
+      <x:c r="B146" t="n">
+        <x:v>3256</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>MARINE_SIX_HITS</x:v>
+      </x:c>
+      <x:c r="D146" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E146" t="str">
+        <x:v>battle.card.marine.six_hits.name</x:v>
+      </x:c>
+      <x:c r="F146" t="str">
+        <x:v>battle.card.marine.six_hits.description</x:v>
+      </x:c>
+      <x:c r="G146" t="str">
+        <x:v>battle.card.marine.six_hits.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H146" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I146" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J146" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K146" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L146" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M146" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N146" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O146" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P146" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q146" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R146"/>
+      <x:c r="S146" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T146" s="27" t="str">
+        <x:v>SixHits</x:v>
+      </x:c>
+      <x:c r="U146" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147"/>
+      <x:c r="B147" t="n">
+        <x:v>3257</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>MARINE_TWELVE_HITS</x:v>
+      </x:c>
+      <x:c r="D147" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E147" t="str">
+        <x:v>battle.card.marine.twelve_hits.name</x:v>
+      </x:c>
+      <x:c r="F147" t="str">
+        <x:v>battle.card.marine.twelve_hits.description</x:v>
+      </x:c>
+      <x:c r="G147" t="str">
+        <x:v>battle.card.marine.twelve_hits.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H147" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I147" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J147" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K147" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L147" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M147" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N147" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O147" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P147" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q147" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R147"/>
+      <x:c r="S147" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T147" s="27" t="str">
+        <x:v>TwelveHits</x:v>
+      </x:c>
+      <x:c r="U147" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148"/>
+      <x:c r="B148" t="n">
+        <x:v>3258</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>MARINE_QUICK_MANEUVER</x:v>
+      </x:c>
+      <x:c r="D148" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E148" t="str">
+        <x:v>battle.card.marine.quick_maneuver.name</x:v>
+      </x:c>
+      <x:c r="F148" t="str">
+        <x:v>battle.card.marine.quick_maneuver.description</x:v>
+      </x:c>
+      <x:c r="G148" t="str">
+        <x:v>battle.card.marine.quick_maneuver.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H148" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I148" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J148" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K148" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L148" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M148" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N148" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O148" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P148" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q148" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R148"/>
+      <x:c r="S148" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T148" s="27" t="str">
+        <x:v>QuickManeuver</x:v>
+      </x:c>
+      <x:c r="U148" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149"/>
+      <x:c r="B149" t="n">
+        <x:v>3259</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>MARINE_HOLO_DECOY</x:v>
+      </x:c>
+      <x:c r="D149" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E149" t="str">
+        <x:v>battle.card.marine.holo_decoy.name</x:v>
+      </x:c>
+      <x:c r="F149" t="str">
+        <x:v>battle.card.marine.holo_decoy.description</x:v>
+      </x:c>
+      <x:c r="G149" t="str">
+        <x:v>battle.card.marine.holo_decoy.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H149" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I149" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K149" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M149" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N149" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="O149" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="P149" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q149" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R149"/>
+      <x:c r="S149" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T149" s="27" t="str">
+        <x:v>HoloDecoy</x:v>
+      </x:c>
+      <x:c r="U149" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150"/>
+      <x:c r="B150" t="n">
+        <x:v>3260</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>MARINE_LIMIT_OVERLOAD</x:v>
+      </x:c>
+      <x:c r="D150" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E150" t="str">
+        <x:v>battle.card.marine.limit_overload.name</x:v>
+      </x:c>
+      <x:c r="F150" t="str">
+        <x:v>battle.card.marine.limit_overload.description</x:v>
+      </x:c>
+      <x:c r="G150" t="str">
+        <x:v>battle.card.marine.limit_overload.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H150" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I150" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K150" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M150" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N150" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O150" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P150" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q150" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R150"/>
+      <x:c r="S150" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T150" s="27" t="str">
+        <x:v>LimitOverload</x:v>
+      </x:c>
+      <x:c r="U150" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151"/>
+      <x:c r="B151" t="n">
+        <x:v>3261</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>MARINE_MACHINEGUN</x:v>
+      </x:c>
+      <x:c r="D151" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E151" t="str">
+        <x:v>battle.card.marine.machinegun.name</x:v>
+      </x:c>
+      <x:c r="F151" t="str">
+        <x:v>battle.card.marine.machinegun.description</x:v>
+      </x:c>
+      <x:c r="G151" t="str">
+        <x:v>battle.card.marine.machinegun.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H151" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I151" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J151" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K151" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L151" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M151" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N151" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="O151" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="P151" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q151" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R151"/>
+      <x:c r="S151" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T151" s="27" t="str">
+        <x:v>Machinegun</x:v>
+      </x:c>
+      <x:c r="U151" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152"/>
+      <x:c r="B152" t="n">
+        <x:v>3262</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>MARINE_DEFENSE_TARGET</x:v>
+      </x:c>
+      <x:c r="D152" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E152" t="str">
+        <x:v>battle.card.marine.defense_target.name</x:v>
+      </x:c>
+      <x:c r="F152" t="str">
+        <x:v>battle.card.marine.defense_target.description</x:v>
+      </x:c>
+      <x:c r="G152" t="str">
+        <x:v>battle.card.marine.defense_target.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H152" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I152" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J152" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K152" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L152" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M152" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N152" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="O152" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="P152" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q152" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R152"/>
+      <x:c r="S152" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T152" s="27" t="str">
+        <x:v>DefenseTarget</x:v>
+      </x:c>
+      <x:c r="U152" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153"/>
+      <x:c r="B153" t="n">
+        <x:v>3263</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>MARINE_MACHINEGUN_BURST</x:v>
+      </x:c>
+      <x:c r="D153" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E153" t="str">
+        <x:v>battle.card.marine.machinegun_burst.name</x:v>
+      </x:c>
+      <x:c r="F153" t="str">
+        <x:v>battle.card.marine.machinegun_burst.description</x:v>
+      </x:c>
+      <x:c r="G153" t="str">
+        <x:v>battle.card.marine.machinegun_burst.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H153" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I153" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K153" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M153" t="str">
+        <x:v>RandomEnemy</x:v>
+      </x:c>
+      <x:c r="N153" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="O153" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="P153" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q153" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R153"/>
+      <x:c r="S153" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T153" s="27" t="str">
+        <x:v>MachinegunBurst</x:v>
+      </x:c>
+      <x:c r="U153" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154"/>
+      <x:c r="B154" t="n">
+        <x:v>3264</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>MARINE_TRIPLE_STRIKE</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
+        <x:v>marine-game-v1-20260807-cards</x:v>
+      </x:c>
+      <x:c r="E154" t="str">
+        <x:v>battle.card.marine.triple_strike.name</x:v>
+      </x:c>
+      <x:c r="F154" t="str">
+        <x:v>battle.card.marine.triple_strike.description</x:v>
+      </x:c>
+      <x:c r="G154" t="str">
+        <x:v>battle.card.marine.triple_strike.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H154" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I154" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J154" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K154" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L154" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M154" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N154" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="O154" t="str">
+        <x:v>ExhaustPile</x:v>
+      </x:c>
+      <x:c r="P154" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q154" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R154"/>
+      <x:c r="S154" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T154" s="27" t="str">
+        <x:v>TripleStrike</x:v>
+      </x:c>
+      <x:c r="U154" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155"/>
+      <x:c r="B155" t="n">
+        <x:v>3265</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>MARINE_BOMBARD</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>battle.card.marine.bombard.name</x:v>
+      </x:c>
+      <x:c r="F155" t="str">
+        <x:v>battle.card.marine.bombard.description</x:v>
+      </x:c>
+      <x:c r="G155" t="str">
+        <x:v>battle.card.marine.bombard.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H155" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I155" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J155" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K155" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L155" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M155" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N155" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O155" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P155" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q155" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R155"/>
+      <x:c r="S155" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T155" t="str">
+        <x:v>Bombard</x:v>
+      </x:c>
+      <x:c r="U155" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156"/>
+      <x:c r="B156" t="n">
+        <x:v>3266</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>MARINE_SKY_WRATH</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>battle.card.marine.sky_wrath.name</x:v>
+      </x:c>
+      <x:c r="F156" t="str">
+        <x:v>battle.card.marine.sky_wrath.description</x:v>
+      </x:c>
+      <x:c r="G156" t="str">
+        <x:v>battle.card.marine.sky_wrath.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H156" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I156" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J156" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K156" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L156" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M156" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N156" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O156" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P156" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q156" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R156"/>
+      <x:c r="S156" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T156" t="str">
+        <x:v>SkyWrath</x:v>
+      </x:c>
+      <x:c r="U156" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157"/>
+      <x:c r="B157" t="n">
+        <x:v>3267</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>MARINE_PORTABLE_HELPER</x:v>
+      </x:c>
+      <x:c r="D157" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E157" t="str">
+        <x:v>battle.card.marine.portable_helper.name</x:v>
+      </x:c>
+      <x:c r="F157" t="str">
+        <x:v>battle.card.marine.portable_helper.description</x:v>
+      </x:c>
+      <x:c r="G157" t="str">
+        <x:v>battle.card.marine.portable_helper.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H157" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I157" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J157" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K157" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M157" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N157" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O157" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P157" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q157" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R157"/>
+      <x:c r="S157" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T157" t="str">
+        <x:v>PortableHelper</x:v>
+      </x:c>
+      <x:c r="U157" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158"/>
+      <x:c r="B158" t="n">
+        <x:v>3268</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>MARINE_PRIVATE_MOD</x:v>
+      </x:c>
+      <x:c r="D158" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E158" t="str">
+        <x:v>battle.card.marine.private_mod.name</x:v>
+      </x:c>
+      <x:c r="F158" t="str">
+        <x:v>battle.card.marine.private_mod.description</x:v>
+      </x:c>
+      <x:c r="G158" t="str">
+        <x:v>battle.card.marine.private_mod.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H158" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="I158" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J158" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K158" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L158" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M158" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N158" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="O158" t="str">
+        <x:v>Power</x:v>
+      </x:c>
+      <x:c r="P158" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q158" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R158"/>
+      <x:c r="S158" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T158" t="str">
+        <x:v>PrivateMod</x:v>
+      </x:c>
+      <x:c r="U158" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159"/>
+      <x:c r="B159" t="n">
+        <x:v>3269</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>MARINE_CHAIN_SMOKE</x:v>
+      </x:c>
+      <x:c r="D159" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E159" t="str">
+        <x:v>battle.card.marine.chain_smoke.name</x:v>
+      </x:c>
+      <x:c r="F159" t="str">
+        <x:v>battle.card.marine.chain_smoke.description</x:v>
+      </x:c>
+      <x:c r="G159" t="str">
+        <x:v>battle.card.marine.chain_smoke.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H159" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I159" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J159" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K159" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L159" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M159" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N159" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O159" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P159" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q159" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R159"/>
+      <x:c r="S159" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T159" t="str">
+        <x:v>ChainSmoke</x:v>
+      </x:c>
+      <x:c r="U159" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160"/>
+      <x:c r="B160" t="n">
+        <x:v>3270</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>MARINE_SECONDHAND_SMOKE</x:v>
+      </x:c>
+      <x:c r="D160" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E160" t="str">
+        <x:v>battle.card.marine.secondhand_smoke.name</x:v>
+      </x:c>
+      <x:c r="F160" t="str">
+        <x:v>battle.card.marine.secondhand_smoke.description</x:v>
+      </x:c>
+      <x:c r="G160" t="str">
+        <x:v>battle.card.marine.secondhand_smoke.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H160" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I160" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J160" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K160" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L160" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M160" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N160" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O160" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P160" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q160" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R160"/>
+      <x:c r="S160" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T160" t="str">
+        <x:v>SecondhandSmoke</x:v>
+      </x:c>
+      <x:c r="U160" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161"/>
+      <x:c r="B161" t="n">
+        <x:v>3271</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>MARINE_DEFENSIVE_STANCE</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E161" t="str">
+        <x:v>battle.card.marine.defensive_stance.name</x:v>
+      </x:c>
+      <x:c r="F161" t="str">
+        <x:v>battle.card.marine.defensive_stance.description</x:v>
+      </x:c>
+      <x:c r="G161" t="str">
+        <x:v>battle.card.marine.defensive_stance.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H161" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I161" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K161" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M161" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N161" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O161" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P161" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q161" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R161"/>
+      <x:c r="S161" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T161" t="str">
+        <x:v>DefensiveStance</x:v>
+      </x:c>
+      <x:c r="U161" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162"/>
+      <x:c r="B162" t="n">
+        <x:v>3272</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>MARINE_EMERGENCY_COOLING</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E162" t="str">
+        <x:v>battle.card.marine.emergency_cooling.name</x:v>
+      </x:c>
+      <x:c r="F162" t="str">
+        <x:v>battle.card.marine.emergency_cooling.description</x:v>
+      </x:c>
+      <x:c r="G162" t="str">
+        <x:v>battle.card.marine.emergency_cooling.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H162" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I162" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J162" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K162" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L162" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M162" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N162" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O162" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P162" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q162" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R162"/>
+      <x:c r="S162" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T162" t="str">
+        <x:v>EmergencyCooling</x:v>
+      </x:c>
+      <x:c r="U162" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163"/>
+      <x:c r="B163" t="n">
+        <x:v>3273</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>MARINE_THERMITE_BOMB</x:v>
+      </x:c>
+      <x:c r="D163" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E163" t="str">
+        <x:v>battle.card.marine.thermite_bomb.name</x:v>
+      </x:c>
+      <x:c r="F163" t="str">
+        <x:v>battle.card.marine.thermite_bomb.description</x:v>
+      </x:c>
+      <x:c r="G163" t="str">
+        <x:v>battle.card.marine.thermite_bomb.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H163" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I163" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J163" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K163" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L163" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M163" t="str">
+        <x:v>AllEnemies</x:v>
+      </x:c>
+      <x:c r="N163" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O163" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P163" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q163" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R163"/>
+      <x:c r="S163" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T163" t="str">
+        <x:v>ThermiteBomb</x:v>
+      </x:c>
+      <x:c r="U163" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164"/>
+      <x:c r="B164" t="n">
+        <x:v>3274</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>MARINE_NEEDLE_STORM</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E164" t="str">
+        <x:v>battle.card.marine.needle_storm.name</x:v>
+      </x:c>
+      <x:c r="F164" t="str">
+        <x:v>battle.card.marine.needle_storm.description</x:v>
+      </x:c>
+      <x:c r="G164" t="str">
+        <x:v>battle.card.marine.needle_storm.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H164" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I164" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J164" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K164" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L164" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M164" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N164" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O164" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P164" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q164" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R164"/>
+      <x:c r="S164" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T164" t="str">
+        <x:v>NeedleStorm</x:v>
+      </x:c>
+      <x:c r="U164" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165"/>
+      <x:c r="B165" t="n">
+        <x:v>3275</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>MARINE_STEALTH_ACTION</x:v>
+      </x:c>
+      <x:c r="D165" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E165" t="str">
+        <x:v>battle.card.marine.stealth_action.name</x:v>
+      </x:c>
+      <x:c r="F165" t="str">
+        <x:v>battle.card.marine.stealth_action.description</x:v>
+      </x:c>
+      <x:c r="G165" t="str">
+        <x:v>battle.card.marine.stealth_action.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H165" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I165" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K165" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L165" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M165" t="str">
+        <x:v>Self</x:v>
+      </x:c>
+      <x:c r="N165" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O165" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P165" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q165" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R165"/>
+      <x:c r="S165" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T165" t="str">
+        <x:v>StealthAction</x:v>
+      </x:c>
+      <x:c r="U165" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166"/>
+      <x:c r="B166" t="n">
+        <x:v>3276</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>MARINE_FOEHN_WIND</x:v>
+      </x:c>
+      <x:c r="D166" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E166" t="str">
+        <x:v>battle.card.marine.foehn_wind.name</x:v>
+      </x:c>
+      <x:c r="F166" t="str">
+        <x:v>battle.card.marine.foehn_wind.description</x:v>
+      </x:c>
+      <x:c r="G166" t="str">
+        <x:v>battle.card.marine.foehn_wind.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H166" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="I166" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J166" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K166" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L166" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M166" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N166" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O166" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P166" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q166" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R166"/>
+      <x:c r="S166" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T166" t="str">
+        <x:v>FoehnWind</x:v>
+      </x:c>
+      <x:c r="U166" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167"/>
+      <x:c r="B167" t="n">
+        <x:v>3277</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>MARINE_PREEMPTIVE_STRIKE</x:v>
+      </x:c>
+      <x:c r="D167" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E167" t="str">
+        <x:v>battle.card.marine.preemptive_strike.name</x:v>
+      </x:c>
+      <x:c r="F167" t="str">
+        <x:v>battle.card.marine.preemptive_strike.description</x:v>
+      </x:c>
+      <x:c r="G167" t="str">
+        <x:v>battle.card.marine.preemptive_strike.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H167" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I167" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J167" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K167" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L167" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M167" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N167" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O167" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P167" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q167" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R167"/>
+      <x:c r="S167" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T167" t="str">
+        <x:v>PreemptiveStrike</x:v>
+      </x:c>
+      <x:c r="U167" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168"/>
+      <x:c r="B168" t="n">
+        <x:v>3278</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>MARINE_BULLY</x:v>
+      </x:c>
+      <x:c r="D168" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E168" t="str">
+        <x:v>battle.card.marine.bully.name</x:v>
+      </x:c>
+      <x:c r="F168" t="str">
+        <x:v>battle.card.marine.bully.description</x:v>
+      </x:c>
+      <x:c r="G168" t="str">
+        <x:v>battle.card.marine.bully.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H168" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I168" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K168" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M168" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N168" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O168" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P168" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q168" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R168"/>
+      <x:c r="S168" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T168" t="str">
+        <x:v>Bully</x:v>
+      </x:c>
+      <x:c r="U168" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169"/>
+      <x:c r="B169" t="n">
+        <x:v>3279</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>MARINE_PRISMATIC_SHOT</x:v>
+      </x:c>
+      <x:c r="D169" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E169" t="str">
+        <x:v>battle.card.marine.prismatic_shot.name</x:v>
+      </x:c>
+      <x:c r="F169" t="str">
+        <x:v>battle.card.marine.prismatic_shot.description</x:v>
+      </x:c>
+      <x:c r="G169" t="str">
+        <x:v>battle.card.marine.prismatic_shot.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H169" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I169" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="J169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K169" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M169" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N169" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O169" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P169" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q169" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R169"/>
+      <x:c r="S169" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T169" t="str">
+        <x:v>PrismaticShot</x:v>
+      </x:c>
+      <x:c r="U169" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170"/>
+      <x:c r="B170" t="n">
+        <x:v>3280</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>MARINE_MARK</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E170" t="str">
+        <x:v>battle.card.marine.mark.name</x:v>
+      </x:c>
+      <x:c r="F170" t="str">
+        <x:v>battle.card.marine.mark.description</x:v>
+      </x:c>
+      <x:c r="G170" t="str">
+        <x:v>battle.card.marine.mark.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H170" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I170" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="J170" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K170" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L170" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M170" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N170" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O170" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P170" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q170" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R170"/>
+      <x:c r="S170" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T170" t="str">
+        <x:v>Mark</x:v>
+      </x:c>
+      <x:c r="U170" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171"/>
+      <x:c r="B171" t="n">
+        <x:v>3281</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>MARINE_CRUSH</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>battle.card.marine.crush.name</x:v>
+      </x:c>
+      <x:c r="F171" t="str">
+        <x:v>battle.card.marine.crush.description</x:v>
+      </x:c>
+      <x:c r="G171" t="str">
+        <x:v>battle.card.marine.crush.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H171" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I171" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J171" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K171" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L171" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M171" t="str">
+        <x:v>Enemy</x:v>
+      </x:c>
+      <x:c r="N171" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O171" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P171" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q171" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R171"/>
+      <x:c r="S171" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T171" t="str">
+        <x:v>Crush</x:v>
+      </x:c>
+      <x:c r="U171" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172"/>
+      <x:c r="B172" t="n">
+        <x:v>3282</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>MARINE_CHARGED_BURST</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
+        <x:v>marine-game-v2-20260812-cards</x:v>
+      </x:c>
+      <x:c r="E172" t="str">
+        <x:v>battle.card.marine.charged_burst.name</x:v>
+      </x:c>
+      <x:c r="F172" t="str">
+        <x:v>battle.card.marine.charged_burst.description</x:v>
+      </x:c>
+      <x:c r="G172" t="str">
+        <x:v>battle.card.marine.charged_burst.upgrade_description</x:v>
+      </x:c>
+      <x:c r="H172" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I172" t="str">
+        <x:v>Uncommon</x:v>
+      </x:c>
+      <x:c r="J172" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K172" t="str">
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="L172" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M172" t="str">
+        <x:v>AllEnemies</x:v>
+      </x:c>
+      <x:c r="N172" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="O172" t="str">
+        <x:v>DiscardPile</x:v>
+      </x:c>
+      <x:c r="P172" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q172" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="R172"/>
+      <x:c r="S172" t="str">
+        <x:v>art_placeholder</x:v>
+      </x:c>
+      <x:c r="T172" t="str">
+        <x:v>ChargedBurst</x:v>
+      </x:c>
+      <x:c r="U172" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/Datas/battle.card.xlsx
+++ b/DataTables/Datas/battle.card.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2eb378f8f274ecd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R772dac778e2a4921"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,6 +555,9 @@
     <x:col min="19" max="19" width="28" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="15" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="24" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="30" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -621,6 +624,15 @@
       <x:c r="U1" s="31" t="str">
         <x:v>is_innate</x:v>
       </x:c>
+      <x:c r="V1" t="str">
+        <x:v>upgrade_track_kind</x:v>
+      </x:c>
+      <x:c r="W1" t="str">
+        <x:v>infinite_upgrade_rule_kind</x:v>
+      </x:c>
+      <x:c r="X1" t="str">
+        <x:v>infinite_upgrade_value_per_level</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="11" t="str">
@@ -685,6 +697,15 @@
       </x:c>
       <x:c r="U2" s="35" t="str">
         <x:v>bool</x:v>
+      </x:c>
+      <x:c r="V2" t="str">
+        <x:v>battle.CardUpgradeTrackKind</x:v>
+      </x:c>
+      <x:c r="W2" t="str">
+        <x:v>battle.CardUpgradeRuleKind</x:v>
+      </x:c>
+      <x:c r="X2" t="str">
+        <x:v>int</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
@@ -711,6 +732,9 @@
       <x:c r="S3" s="12"/>
       <x:c r="T3" s="24"/>
       <x:c r="U3"/>
+      <x:c r="V3"/>
+      <x:c r="W3"/>
+      <x:c r="X3"/>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="14" t="str">
@@ -775,6 +799,15 @@
       </x:c>
       <x:c r="U4" s="39" t="str">
         <x:v>Whether the card is innate</x:v>
+      </x:c>
+      <x:c r="V4" t="str">
+        <x:v>G4 upgrade track</x:v>
+      </x:c>
+      <x:c r="W4" t="str">
+        <x:v>Typed infinite upgrade rule</x:v>
+      </x:c>
+      <x:c r="X4" t="str">
+        <x:v>Typed value added per upgrade level</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
@@ -839,6 +872,15 @@
       <x:c r="U5" s="43" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V5" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W5" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X5" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="12"/>
@@ -902,6 +944,15 @@
       <x:c r="U6" s="43" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V6" t="str">
+        <x:v>Finite</x:v>
+      </x:c>
+      <x:c r="W6" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="12"/>
@@ -965,6 +1016,15 @@
       <x:c r="U7" s="43" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V7" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W7" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X7" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="12"/>
@@ -1028,6 +1088,15 @@
       <x:c r="U8" s="43" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V8" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W8" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X8" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="16"/>
@@ -1089,6 +1158,15 @@
       <x:c r="U9" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V9" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W9" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X9" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="16"/>
@@ -1150,6 +1228,15 @@
       <x:c r="U10" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V10" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W10" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X10" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="16"/>
@@ -1211,6 +1298,15 @@
       <x:c r="U11" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V11" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W11" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X11" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="16"/>
@@ -1272,6 +1368,15 @@
       <x:c r="U12" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V12" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W12" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X12" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="16"/>
@@ -1335,6 +1440,15 @@
       <x:c r="U13" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V13" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W13" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X13" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
       <x:c r="A14" s="16"/>
@@ -1396,6 +1510,15 @@
       <x:c r="U14" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
       <x:c r="A15" s="16"/>
@@ -1457,6 +1580,15 @@
       <x:c r="U15" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V15" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W15" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X15" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
       <x:c r="A16" s="16"/>
@@ -1520,6 +1652,15 @@
       <x:c r="U16" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V16" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W16" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="22" customHeight="1">
       <x:c r="A17" s="16"/>
@@ -1581,6 +1722,15 @@
       <x:c r="U17" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V17" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W17" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X17" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
       <x:c r="A18" s="16"/>
@@ -1642,6 +1792,15 @@
       <x:c r="U18" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V18" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W18" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X18" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
       <x:c r="A19" s="16"/>
@@ -1703,6 +1862,15 @@
       <x:c r="U19" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V19" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W19" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X19" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" s="16"/>
@@ -1764,6 +1932,15 @@
       <x:c r="U20" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V20" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W20" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X20" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" s="16"/>
@@ -1827,6 +2004,15 @@
       <x:c r="U21" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V21" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W21" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X21" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
       <x:c r="A22" s="16"/>
@@ -1888,6 +2074,15 @@
       <x:c r="U22" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V22" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W22" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X22" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
       <x:c r="A23" s="16"/>
@@ -1951,6 +2146,15 @@
       <x:c r="U23" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V23" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W23" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X23" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
       <x:c r="A24" s="16"/>
@@ -2014,6 +2218,15 @@
       <x:c r="U24" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V24" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W24" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X24" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="22" customHeight="1">
       <x:c r="A25" s="16"/>
@@ -2075,6 +2288,15 @@
       <x:c r="U25" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X25" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
       <x:c r="A26" s="16"/>
@@ -2138,6 +2360,15 @@
       <x:c r="U26" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V26" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W26" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X26" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
       <x:c r="A27" s="16"/>
@@ -2199,6 +2430,15 @@
       <x:c r="U27" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X27" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
       <x:c r="A28" s="16"/>
@@ -2262,6 +2502,15 @@
       <x:c r="U28" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V28" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W28" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X28" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="22" customHeight="1">
       <x:c r="A29" s="16"/>
@@ -2323,6 +2572,15 @@
       <x:c r="U29" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V29" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W29" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X29" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
       <x:c r="A30" s="16"/>
@@ -2384,6 +2642,15 @@
       <x:c r="U30" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V30" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W30" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X30" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" s="16"/>
@@ -2447,6 +2714,15 @@
       <x:c r="U31" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V31" t="str">
+        <x:v>Infinite</x:v>
+      </x:c>
+      <x:c r="W31" t="str">
+        <x:v>DamageValue</x:v>
+      </x:c>
+      <x:c r="X31" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
       <x:c r="A32" s="16"/>
@@ -2508,6 +2784,15 @@
       <x:c r="U32" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W32" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X32" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" s="16"/>
@@ -2571,6 +2856,15 @@
       <x:c r="U33" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V33" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W33" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X33" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
       <x:c r="A34" s="16"/>
@@ -2632,6 +2926,15 @@
       <x:c r="U34" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V34" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W34" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X34" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="22" customHeight="1">
       <x:c r="A35" s="16"/>
@@ -2693,6 +2996,15 @@
       <x:c r="U35" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V35" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W35" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X35" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="16"/>
@@ -2754,6 +3066,15 @@
       <x:c r="U36" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V36" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W36" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X36" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="22" customHeight="1">
       <x:c r="A37" s="16"/>
@@ -2815,6 +3136,15 @@
       <x:c r="U37" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V37" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W37" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="22" customHeight="1">
       <x:c r="A38" s="16"/>
@@ -2876,6 +3206,15 @@
       <x:c r="U38" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V38" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W38" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X38" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="22" customHeight="1">
       <x:c r="A39" s="16"/>
@@ -2937,6 +3276,15 @@
       <x:c r="U39" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V39" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W39" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X39" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="22" customHeight="1">
       <x:c r="A40" s="16"/>
@@ -2998,6 +3346,15 @@
       <x:c r="U40" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V40" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W40" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X40" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="22" customHeight="1">
       <x:c r="A41" s="16"/>
@@ -3059,6 +3416,15 @@
       <x:c r="U41" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V41" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W41" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X41" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="22" customHeight="1">
       <x:c r="A42" s="16"/>
@@ -3120,6 +3486,15 @@
       <x:c r="U42" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V42" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W42" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X42" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="22" customHeight="1">
       <x:c r="A43" s="16"/>
@@ -3181,6 +3556,15 @@
       <x:c r="U43" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V43" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W43" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X43" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="22" customHeight="1">
       <x:c r="A44" s="16"/>
@@ -3242,6 +3626,15 @@
       <x:c r="U44" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V44" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W44" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X44" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="22" customHeight="1">
       <x:c r="A45" s="16"/>
@@ -3303,6 +3696,15 @@
       <x:c r="U45" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V45" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W45" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X45" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="22" customHeight="1">
       <x:c r="A46" s="16"/>
@@ -3364,6 +3766,15 @@
       <x:c r="U46" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V46" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W46" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X46" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="22" customHeight="1">
       <x:c r="A47" s="16"/>
@@ -3425,6 +3836,15 @@
       <x:c r="U47" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V47" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W47" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X47" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="22" customHeight="1">
       <x:c r="A48" s="16"/>
@@ -3486,6 +3906,15 @@
       <x:c r="U48" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V48" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W48" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X48" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="22" customHeight="1">
       <x:c r="A49" s="16"/>
@@ -3547,6 +3976,15 @@
       <x:c r="U49" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V49" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W49" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="22" customHeight="1">
       <x:c r="A50" s="16"/>
@@ -3608,6 +4046,15 @@
       <x:c r="U50" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V50" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W50" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X50" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="22" customHeight="1">
       <x:c r="A51" s="16"/>
@@ -3669,6 +4116,15 @@
       <x:c r="U51" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X51" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="22" customHeight="1">
       <x:c r="A52" s="16"/>
@@ -3730,6 +4186,15 @@
       <x:c r="U52" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V52" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W52" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X52" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="22" customHeight="1">
       <x:c r="A53" s="16"/>
@@ -3791,6 +4256,15 @@
       <x:c r="U53" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V53" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W53" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X53" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
       <x:c r="A54" s="16"/>
@@ -3852,6 +4326,15 @@
       <x:c r="U54" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V54" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W54" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X54" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="22" customHeight="1">
       <x:c r="A55" s="16"/>
@@ -3913,6 +4396,15 @@
       <x:c r="U55" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V55" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W55" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X55" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="22" customHeight="1">
       <x:c r="A56" s="16"/>
@@ -3974,6 +4466,15 @@
       <x:c r="U56" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V56" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W56" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X56" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="22" customHeight="1">
       <x:c r="A57" s="16"/>
@@ -4035,6 +4536,15 @@
       <x:c r="U57" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V57" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W57" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X57" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="22" customHeight="1">
       <x:c r="A58" s="16"/>
@@ -4096,6 +4606,15 @@
       <x:c r="U58" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V58" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W58" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X58" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
       <x:c r="A59" s="16"/>
@@ -4157,6 +4676,15 @@
       <x:c r="U59" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V59" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W59" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X59" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="22" customHeight="1">
       <x:c r="A60" s="16"/>
@@ -4218,6 +4746,15 @@
       <x:c r="U60" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V60" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W60" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X60" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="22" customHeight="1">
       <x:c r="A61" s="16"/>
@@ -4279,6 +4816,15 @@
       <x:c r="U61" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V61" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W61" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X61" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="22" customHeight="1">
       <x:c r="A62" s="16"/>
@@ -4340,6 +4886,15 @@
       <x:c r="U62" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V62" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W62" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X62" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="22" customHeight="1">
       <x:c r="A63" s="16"/>
@@ -4401,6 +4956,15 @@
       <x:c r="U63" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V63" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W63" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X63" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="22" customHeight="1">
       <x:c r="A64" s="16"/>
@@ -4462,6 +5026,15 @@
       <x:c r="U64" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V64" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W64" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X64" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="22" customHeight="1">
       <x:c r="A65" s="16"/>
@@ -4525,6 +5098,15 @@
       <x:c r="U65" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V65" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W65" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X65" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="22" customHeight="1">
       <x:c r="A66" s="16"/>
@@ -4586,6 +5168,15 @@
       <x:c r="U66" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V66" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W66" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X66" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="22" customHeight="1">
       <x:c r="A67" s="16"/>
@@ -4647,6 +5238,15 @@
       <x:c r="U67" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V67" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W67" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X67" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="22" customHeight="1">
       <x:c r="A68" s="16"/>
@@ -4708,6 +5308,15 @@
       <x:c r="U68" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V68" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W68" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X68" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="22" customHeight="1">
       <x:c r="A69" s="16"/>
@@ -4769,6 +5378,15 @@
       <x:c r="U69" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V69" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W69" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X69" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="22" customHeight="1">
       <x:c r="A70" s="16"/>
@@ -4830,6 +5448,15 @@
       <x:c r="U70" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V70" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W70" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X70" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="22" customHeight="1">
       <x:c r="A71" s="16"/>
@@ -4891,6 +5518,15 @@
       <x:c r="U71" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V71" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W71" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X71" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="22" customHeight="1">
       <x:c r="A72" s="16"/>
@@ -4952,6 +5588,15 @@
       <x:c r="U72" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V72" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W72" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X72" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="22" customHeight="1">
       <x:c r="A73" s="16"/>
@@ -5013,6 +5658,15 @@
       <x:c r="U73" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V73" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W73" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X73" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="22" customHeight="1">
       <x:c r="A74" s="16"/>
@@ -5074,6 +5728,15 @@
       <x:c r="U74" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V74" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W74" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X74" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="22" customHeight="1">
       <x:c r="A75" s="16"/>
@@ -5135,6 +5798,15 @@
       <x:c r="U75" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V75" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W75" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X75" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="22" customHeight="1">
       <x:c r="A76" s="16"/>
@@ -5196,6 +5868,15 @@
       <x:c r="U76" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V76" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W76" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X76" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="22" customHeight="1">
       <x:c r="A77" s="16"/>
@@ -5259,6 +5940,15 @@
       <x:c r="U77" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V77" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W77" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X77" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="22" customHeight="1">
       <x:c r="A78" s="16"/>
@@ -5320,6 +6010,15 @@
       <x:c r="U78" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V78" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W78" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X78" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="22" customHeight="1">
       <x:c r="A79" s="16"/>
@@ -5383,6 +6082,15 @@
       <x:c r="U79" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V79" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W79" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X79" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="22" customHeight="1">
       <x:c r="A80" s="16"/>
@@ -5444,6 +6152,15 @@
       <x:c r="U80" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V80" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W80" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X80" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="22" customHeight="1">
       <x:c r="A81" s="16"/>
@@ -5505,6 +6222,15 @@
       <x:c r="U81" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V81" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W81" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X81" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="22" customHeight="1">
       <x:c r="A82" s="16"/>
@@ -5566,6 +6292,15 @@
       <x:c r="U82" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V82" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W82" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X82" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="22" customHeight="1">
       <x:c r="A83" s="16"/>
@@ -5627,6 +6362,15 @@
       <x:c r="U83" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V83" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W83" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X83" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="22" customHeight="1">
       <x:c r="A84" s="16"/>
@@ -5688,6 +6432,15 @@
       <x:c r="U84" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V84" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W84" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X84" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="22" customHeight="1">
       <x:c r="A85" s="16"/>
@@ -5749,6 +6502,15 @@
       <x:c r="U85" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V85" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W85" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X85" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="22" customHeight="1">
       <x:c r="A86" s="16"/>
@@ -5810,6 +6572,15 @@
       <x:c r="U86" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V86" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W86" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X86" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="22" customHeight="1">
       <x:c r="A87" s="16"/>
@@ -5871,6 +6642,15 @@
       <x:c r="U87" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V87" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W87" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X87" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="22" customHeight="1">
       <x:c r="A88" s="16"/>
@@ -5932,6 +6712,15 @@
       <x:c r="U88" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V88" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W88" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X88" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="22" customHeight="1">
       <x:c r="A89" s="16"/>
@@ -5993,6 +6782,15 @@
       <x:c r="U89" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V89" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W89" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X89" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="22" customHeight="1">
       <x:c r="A90" s="16"/>
@@ -6054,6 +6852,15 @@
       <x:c r="U90" s="47" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V90" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W90" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X90" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91"/>
@@ -6115,6 +6922,15 @@
       <x:c r="U91" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V91" t="str">
+        <x:v>Infinite</x:v>
+      </x:c>
+      <x:c r="W91" t="str">
+        <x:v>DamageValue</x:v>
+      </x:c>
+      <x:c r="X91" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92"/>
@@ -6176,6 +6992,15 @@
       <x:c r="U92" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V92" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W92" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X92" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93"/>
@@ -6237,6 +7062,15 @@
       <x:c r="U93" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V93" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W93" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X93" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94"/>
@@ -6298,6 +7132,15 @@
       <x:c r="U94" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V94" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W94" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X94" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95"/>
@@ -6359,6 +7202,15 @@
       <x:c r="U95" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V95" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W95" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X95" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96"/>
@@ -6420,6 +7272,15 @@
       <x:c r="U96" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V96" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W96" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X96" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97"/>
@@ -6481,6 +7342,15 @@
       <x:c r="U97" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V97" t="str">
+        <x:v>Finite</x:v>
+      </x:c>
+      <x:c r="W97" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X97" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98"/>
@@ -6542,6 +7412,15 @@
       <x:c r="U98" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V98" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W98" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X98" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99"/>
@@ -6603,6 +7482,15 @@
       <x:c r="U99" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V99" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W99" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X99" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100"/>
@@ -6664,6 +7552,15 @@
       <x:c r="U100" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V100" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W100" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X100" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101"/>
@@ -6725,6 +7622,15 @@
       <x:c r="U101" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V101" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W101" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X101" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102"/>
@@ -6786,6 +7692,15 @@
       <x:c r="U102" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V102" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W102" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X102" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103"/>
@@ -6847,6 +7762,15 @@
       <x:c r="U103" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V103" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W103" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X103" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104"/>
@@ -6908,6 +7832,15 @@
       <x:c r="U104" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V104" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W104" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X104" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105"/>
@@ -6969,6 +7902,15 @@
       <x:c r="U105" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V105" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W105" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X105" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106"/>
@@ -7030,6 +7972,15 @@
       <x:c r="U106" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V106" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W106" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X106" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107"/>
@@ -7091,6 +8042,15 @@
       <x:c r="U107" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V107" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W107" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X107" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108"/>
@@ -7152,6 +8112,15 @@
       <x:c r="U108" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V108" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W108" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X108" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109"/>
@@ -7213,6 +8182,15 @@
       <x:c r="U109" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V109" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W109" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X109" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110"/>
@@ -7274,6 +8252,15 @@
       <x:c r="U110" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V110" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W110" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X110" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111"/>
@@ -7335,6 +8322,15 @@
       <x:c r="U111" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V111" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W111" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X111" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112"/>
@@ -7396,6 +8392,15 @@
       <x:c r="U112" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V112" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W112" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X112" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113"/>
@@ -7457,6 +8462,15 @@
       <x:c r="U113" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V113" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W113" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X113" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114"/>
@@ -7518,6 +8532,15 @@
       <x:c r="U114" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V114" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W114" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X114" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115"/>
@@ -7579,6 +8602,15 @@
       <x:c r="U115" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V115" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W115" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X115" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116"/>
@@ -7640,6 +8672,15 @@
       <x:c r="U116" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V116" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W116" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X116" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117"/>
@@ -7701,6 +8742,15 @@
       <x:c r="U117" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V117" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W117" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X117" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118"/>
@@ -7762,6 +8812,15 @@
       <x:c r="U118" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V118" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W118" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X118" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119"/>
@@ -7823,6 +8882,15 @@
       <x:c r="U119" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V119" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W119" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X119" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120"/>
@@ -7884,6 +8952,15 @@
       <x:c r="U120" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V120" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W120" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X120" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121"/>
@@ -7945,6 +9022,15 @@
       <x:c r="U121" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V121" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W121" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X121" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122"/>
@@ -8006,6 +9092,15 @@
       <x:c r="U122" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V122" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W122" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X122" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123"/>
@@ -8067,6 +9162,15 @@
       <x:c r="U123" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V123" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W123" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X123" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124"/>
@@ -8128,6 +9232,15 @@
       <x:c r="U124" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V124" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W124" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X124" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125"/>
@@ -8189,6 +9302,15 @@
       <x:c r="U125" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V125" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W125" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X125" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126"/>
@@ -8250,6 +9372,15 @@
       <x:c r="U126" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V126" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W126" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X126" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127"/>
@@ -8311,6 +9442,15 @@
       <x:c r="U127" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V127" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W127" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X127" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128"/>
@@ -8372,6 +9512,15 @@
       <x:c r="U128" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V128" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W128" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X128" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129"/>
@@ -8433,6 +9582,15 @@
       <x:c r="U129" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V129" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W129" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X129" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130"/>
@@ -8494,6 +9652,15 @@
       <x:c r="U130" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V130" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W130" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X130" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131"/>
@@ -8555,6 +9722,15 @@
       <x:c r="U131" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V131" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W131" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X131" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132"/>
@@ -8616,6 +9792,15 @@
       <x:c r="U132" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V132" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W132" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X132" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133"/>
@@ -8677,6 +9862,15 @@
       <x:c r="U133" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V133" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W133" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X133" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134"/>
@@ -8738,6 +9932,15 @@
       <x:c r="U134" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V134" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W134" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X134" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135"/>
@@ -8799,6 +10002,15 @@
       <x:c r="U135" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V135" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W135" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X135" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="136">
       <x:c r="A136"/>
@@ -8860,6 +10072,15 @@
       <x:c r="U136" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V136" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W136" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X136" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137"/>
@@ -8921,6 +10142,15 @@
       <x:c r="U137" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V137" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W137" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X137" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138"/>
@@ -8982,6 +10212,15 @@
       <x:c r="U138" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V138" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W138" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X138" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139"/>
@@ -9043,6 +10282,15 @@
       <x:c r="U139" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V139" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W139" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X139" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140"/>
@@ -9104,6 +10352,15 @@
       <x:c r="U140" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V140" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W140" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X140" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141"/>
@@ -9165,6 +10422,15 @@
       <x:c r="U141" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V141" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W141" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X141" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142"/>
@@ -9226,6 +10492,15 @@
       <x:c r="U142" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V142" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W142" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X142" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143"/>
@@ -9287,6 +10562,15 @@
       <x:c r="U143" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V143" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W143" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X143" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144"/>
@@ -9348,6 +10632,15 @@
       <x:c r="U144" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V144" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W144" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X144" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145"/>
@@ -9409,6 +10702,15 @@
       <x:c r="U145" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V145" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W145" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X145" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146"/>
@@ -9470,6 +10772,15 @@
       <x:c r="U146" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V146" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W146" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X146" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="147">
       <x:c r="A147"/>
@@ -9531,6 +10842,15 @@
       <x:c r="U147" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V147" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W147" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X147" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="148">
       <x:c r="A148"/>
@@ -9592,6 +10912,15 @@
       <x:c r="U148" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V148" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W148" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X148" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149"/>
@@ -9653,6 +10982,15 @@
       <x:c r="U149" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V149" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W149" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X149" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150"/>
@@ -9714,6 +11052,15 @@
       <x:c r="U150" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V150" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W150" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X150" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151"/>
@@ -9775,6 +11122,15 @@
       <x:c r="U151" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V151" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W151" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X151" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152"/>
@@ -9836,6 +11192,15 @@
       <x:c r="U152" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V152" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W152" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X152" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153"/>
@@ -9897,6 +11262,15 @@
       <x:c r="U153" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V153" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W153" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X153" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154"/>
@@ -9958,6 +11332,15 @@
       <x:c r="U154" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V154" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W154" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X154" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155"/>
@@ -10019,6 +11402,15 @@
       <x:c r="U155" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V155" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W155" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X155" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156"/>
@@ -10080,6 +11472,15 @@
       <x:c r="U156" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V156" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W156" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X156" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
       <x:c r="A157"/>
@@ -10141,6 +11542,15 @@
       <x:c r="U157" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V157" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W157" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X157" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158"/>
@@ -10202,6 +11612,15 @@
       <x:c r="U158" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V158" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W158" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X158" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159"/>
@@ -10263,6 +11682,15 @@
       <x:c r="U159" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V159" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W159" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X159" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="160">
       <x:c r="A160"/>
@@ -10324,6 +11752,15 @@
       <x:c r="U160" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V160" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W160" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X160" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161"/>
@@ -10385,6 +11822,15 @@
       <x:c r="U161" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V161" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W161" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X161" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="162">
       <x:c r="A162"/>
@@ -10446,6 +11892,15 @@
       <x:c r="U162" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V162" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W162" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X162" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="163">
       <x:c r="A163"/>
@@ -10507,6 +11962,15 @@
       <x:c r="U163" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V163" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W163" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X163" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164"/>
@@ -10568,6 +12032,15 @@
       <x:c r="U164" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V164" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W164" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X164" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165"/>
@@ -10629,6 +12102,15 @@
       <x:c r="U165" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="V165" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W165" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X165" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="166">
       <x:c r="A166"/>
@@ -10690,6 +12172,15 @@
       <x:c r="U166" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V166" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W166" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X166" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="167">
       <x:c r="A167"/>
@@ -10751,6 +12242,15 @@
       <x:c r="U167" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V167" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W167" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X167" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168"/>
@@ -10812,6 +12312,15 @@
       <x:c r="U168" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V168" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W168" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X168" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="169">
       <x:c r="A169"/>
@@ -10873,6 +12382,15 @@
       <x:c r="U169" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V169" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W169" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X169" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="170">
       <x:c r="A170"/>
@@ -10934,6 +12452,15 @@
       <x:c r="U170" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V170" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W170" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X170" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="171">
       <x:c r="A171"/>
@@ -10995,6 +12522,15 @@
       <x:c r="U171" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V171" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W171" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X171" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="172">
       <x:c r="A172"/>
@@ -11056,6 +12592,15 @@
       <x:c r="U172" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V172" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W172" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="X172" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
